--- a/Master/KODE DAN RESTO BOM NEW.xlsx
+++ b/Master/KODE DAN RESTO BOM NEW.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{983208A8-08E1-45D0-8FF9-8C41A1249DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F980E06-5B7A-4A8A-88EF-64F7723848CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{2A27DFF0-1BDB-46C7-8D34-C6B2AB0C8283}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{2A27DFF0-1BDB-46C7-8D34-C6B2AB0C8283}"/>
   </bookViews>
   <sheets>
     <sheet name="KODE" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="173">
   <si>
     <t>NO</t>
   </si>
@@ -547,6 +547,15 @@
   </si>
   <si>
     <t>Branch</t>
+  </si>
+  <si>
+    <t>TNAKRA</t>
+  </si>
+  <si>
+    <t>1373.1-G.Jakpus - Kramat Raya (TNAKRA)</t>
+  </si>
+  <si>
+    <t>1373.TNAKRA</t>
   </si>
 </sst>
 </file>
@@ -1221,7 +1230,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0933A7F-4C29-4A64-8B36-B4F9E885B333}">
-  <dimension ref="A1:F51"/>
+  <dimension ref="A1:F52"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="12.08984375" bestFit="1" customWidth="1"/>
@@ -2300,6 +2309,26 @@
         <v>166</v>
       </c>
     </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A52" s="2">
+        <v>51</v>
+      </c>
+      <c r="B52" s="13" t="s">
+        <v>70</v>
+      </c>
+      <c r="C52" s="13" t="s">
+        <v>170</v>
+      </c>
+      <c r="D52" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="E52" s="11">
+        <v>46168</v>
+      </c>
+      <c r="F52" s="5" t="s">
+        <v>172</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Master/KODE DAN RESTO BOM NEW.xlsx
+++ b/Master/KODE DAN RESTO BOM NEW.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\GIS\GIS_ESB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F980E06-5B7A-4A8A-88EF-64F7723848CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CE6950B-37FB-4887-B490-218E087BFBA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{2A27DFF0-1BDB-46C7-8D34-C6B2AB0C8283}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{2A27DFF0-1BDB-46C7-8D34-C6B2AB0C8283}"/>
   </bookViews>
   <sheets>
     <sheet name="KODE" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="195">
   <si>
     <t>NO</t>
   </si>
@@ -51,9 +51,6 @@
     <t>STORE</t>
   </si>
   <si>
-    <t xml:space="preserve">START COVER </t>
-  </si>
-  <si>
     <t>JAWA BARAT 1</t>
   </si>
   <si>
@@ -556,6 +553,75 @@
   </si>
   <si>
     <t>1373.TNAKRA</t>
+  </si>
+  <si>
+    <t>1151.GGPDAA</t>
+  </si>
+  <si>
+    <t>1166.GGPPAN</t>
+  </si>
+  <si>
+    <t>1213.GGPJAT</t>
+  </si>
+  <si>
+    <t>1267.GGPPET</t>
+  </si>
+  <si>
+    <t>1368.GGPJOG</t>
+  </si>
+  <si>
+    <t>1049.DPKMAR</t>
+  </si>
+  <si>
+    <t>1073.DPKJAS</t>
+  </si>
+  <si>
+    <t>1092.DPKSAW</t>
+  </si>
+  <si>
+    <t>1104.DPKBOJ</t>
+  </si>
+  <si>
+    <t>1155.DPKPAR</t>
+  </si>
+  <si>
+    <t>1345.DPKLIM</t>
+  </si>
+  <si>
+    <t>1049.1-G.Depok - Margonda (DPKMAR)</t>
+  </si>
+  <si>
+    <t>1073.1-G.Depok - Komjen Pol Jasin (DPKJAS)</t>
+  </si>
+  <si>
+    <t>1092.1-G.Depok - Raya Sawangan (DPKSAW)</t>
+  </si>
+  <si>
+    <t>1104.1-G.Depok - Raya Bojongsari (DPKBOJ)</t>
+  </si>
+  <si>
+    <t>1151.1-G.Jakbar - Raya Daan Mogot (GGPDAA)</t>
+  </si>
+  <si>
+    <t>1155.1-G.Depok - Raya Parung (DPKPAR)</t>
+  </si>
+  <si>
+    <t>1166.1-G.Jakbar - Panjang (GGPPAN)</t>
+  </si>
+  <si>
+    <t>1213.1-G.Jakbar - Tomang Kel. Jatipulo (GGPJAT)</t>
+  </si>
+  <si>
+    <t>1267.1-G.Jakbar - Peta Utara (GGPPET)</t>
+  </si>
+  <si>
+    <t>1345.1-G.Depok - Limo Raya (DPKLIM)</t>
+  </si>
+  <si>
+    <t>1368.1-G.Jakbar - Joglo Raya (GGPJOG)</t>
+  </si>
+  <si>
+    <t>START COVER</t>
   </si>
 </sst>
 </file>
@@ -714,7 +780,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -761,6 +827,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1088,10 +1157,10 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="17" t="s">
+        <v>166</v>
+      </c>
+      <c r="B1" s="16" t="s">
         <v>167</v>
-      </c>
-      <c r="B1" s="16" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
@@ -1230,7 +1299,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0933A7F-4C29-4A64-8B36-B4F9E885B333}">
-  <dimension ref="A1:F52"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="12.08984375" bestFit="1" customWidth="1"/>
@@ -1254,10 +1323,10 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>4</v>
+        <v>194</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
@@ -1265,19 +1334,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>6</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>7</v>
       </c>
       <c r="E2" s="4">
         <v>46062</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -1286,19 +1355,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="E3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>11</v>
-      </c>
       <c r="F3" s="5" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.35">
@@ -1307,19 +1376,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="E4" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="2" t="s">
-        <v>14</v>
-      </c>
       <c r="F4" s="5" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -1328,19 +1397,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C5" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>16</v>
-      </c>
       <c r="E5" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.35">
@@ -1349,19 +1418,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C6" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="E6" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="F6" s="5" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.35">
@@ -1370,19 +1439,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="D7" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="E7" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>22</v>
-      </c>
       <c r="F7" s="5" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.35">
@@ -1391,19 +1460,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C8" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D8" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="E8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="F8" s="5" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.35">
@@ -1412,19 +1481,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C9" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D9" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="E9" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E9" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="F9" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.35">
@@ -1433,19 +1502,19 @@
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>30</v>
-      </c>
       <c r="E10" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -1454,19 +1523,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C11" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>32</v>
-      </c>
       <c r="E11" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.35">
@@ -1475,19 +1544,19 @@
         <v>11</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C12" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="D12" s="7" t="s">
-        <v>34</v>
-      </c>
       <c r="E12" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.35">
@@ -1496,19 +1565,19 @@
         <v>12</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="7" t="s">
-        <v>36</v>
-      </c>
       <c r="E13" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
@@ -1517,19 +1586,19 @@
         <v>13</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C14" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="7" t="s">
-        <v>38</v>
-      </c>
       <c r="E14" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
@@ -1538,19 +1607,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C15" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="7" t="s">
-        <v>40</v>
-      </c>
       <c r="E15" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.35">
@@ -1559,19 +1628,19 @@
         <v>15</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C16" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="7" t="s">
-        <v>42</v>
-      </c>
       <c r="E16" s="2" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.35">
@@ -1580,19 +1649,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C17" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="E17" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E17" s="2" t="s">
-        <v>45</v>
-      </c>
       <c r="F17" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.35">
@@ -1601,19 +1670,19 @@
         <v>17</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C18" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="8" t="s">
         <v>46</v>
       </c>
-      <c r="D18" s="8" t="s">
-        <v>47</v>
-      </c>
       <c r="E18" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.35">
@@ -1622,19 +1691,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C19" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="D19" s="8" t="s">
-        <v>49</v>
-      </c>
       <c r="E19" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.35">
@@ -1643,19 +1712,19 @@
         <v>19</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C20" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="8" t="s">
         <v>50</v>
       </c>
-      <c r="D20" s="8" t="s">
-        <v>51</v>
-      </c>
       <c r="E20" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.35">
@@ -1664,19 +1733,19 @@
         <v>20</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C21" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" s="8" t="s">
         <v>52</v>
       </c>
-      <c r="D21" s="8" t="s">
-        <v>53</v>
-      </c>
       <c r="E21" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.35">
@@ -1685,19 +1754,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C22" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D22" s="8" t="s">
-        <v>55</v>
-      </c>
       <c r="E22" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.35">
@@ -1706,19 +1775,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C23" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="8" t="s">
         <v>56</v>
       </c>
-      <c r="D23" s="8" t="s">
-        <v>57</v>
-      </c>
       <c r="E23" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
@@ -1727,19 +1796,19 @@
         <v>23</v>
       </c>
       <c r="B24" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C24" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="D24" s="8" t="s">
-        <v>59</v>
-      </c>
       <c r="E24" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
@@ -1748,19 +1817,19 @@
         <v>24</v>
       </c>
       <c r="B25" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C25" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D25" s="8" t="s">
         <v>60</v>
       </c>
-      <c r="D25" s="8" t="s">
-        <v>61</v>
-      </c>
       <c r="E25" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
@@ -1769,19 +1838,19 @@
         <v>25</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C26" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="D26" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="D26" s="8" t="s">
-        <v>63</v>
-      </c>
       <c r="E26" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
@@ -1790,19 +1859,19 @@
         <v>26</v>
       </c>
       <c r="B27" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C27" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="D27" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="D27" s="8" t="s">
-        <v>65</v>
-      </c>
       <c r="E27" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.35">
@@ -1811,19 +1880,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C28" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="D28" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="D28" s="8" t="s">
-        <v>67</v>
-      </c>
       <c r="E28" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.35">
@@ -1832,19 +1901,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C29" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="D29" s="8" t="s">
         <v>68</v>
       </c>
-      <c r="D29" s="8" t="s">
-        <v>69</v>
-      </c>
       <c r="E29" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.35">
@@ -1853,19 +1922,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="C30" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="D30" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D30" s="9" t="s">
-        <v>72</v>
-      </c>
       <c r="E30" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.35">
@@ -1874,19 +1943,19 @@
         <v>30</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C31" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D31" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="D31" s="9" t="s">
-        <v>74</v>
-      </c>
       <c r="E31" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.35">
@@ -1895,19 +1964,19 @@
         <v>31</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C32" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="D32" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="D32" s="9" t="s">
-        <v>76</v>
-      </c>
       <c r="E32" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.35">
@@ -1916,19 +1985,19 @@
         <v>32</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C33" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="D33" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="D33" s="9" t="s">
-        <v>78</v>
-      </c>
       <c r="E33" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.35">
@@ -1937,19 +2006,19 @@
         <v>33</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C34" s="9" t="s">
+        <v>78</v>
+      </c>
+      <c r="D34" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="D34" s="9" t="s">
-        <v>80</v>
-      </c>
       <c r="E34" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.35">
@@ -1958,19 +2027,19 @@
         <v>34</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C35" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="D35" s="9" t="s">
         <v>81</v>
       </c>
-      <c r="D35" s="9" t="s">
-        <v>82</v>
-      </c>
       <c r="E35" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.35">
@@ -1979,19 +2048,19 @@
         <v>35</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C36" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D36" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="D36" s="10" t="s">
+      <c r="E36" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="E36" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="F36" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.35">
@@ -2000,19 +2069,19 @@
         <v>36</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C37" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="D37" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="D37" s="10" t="s">
-        <v>87</v>
-      </c>
       <c r="E37" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.35">
@@ -2021,19 +2090,19 @@
         <v>37</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C38" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="D38" s="10" t="s">
         <v>88</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>89</v>
       </c>
       <c r="E38" s="11">
         <v>46027</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.35">
@@ -2042,19 +2111,19 @@
         <v>38</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C39" s="10" t="s">
+        <v>89</v>
+      </c>
+      <c r="D39" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="D39" s="10" t="s">
-        <v>91</v>
-      </c>
       <c r="E39" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.35">
@@ -2063,19 +2132,19 @@
         <v>39</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C40" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="D40" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="D40" s="10" t="s">
+      <c r="E40" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E40" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="F40" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.35">
@@ -2084,19 +2153,19 @@
         <v>40</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C41" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="D41" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="D41" s="10" t="s">
-        <v>96</v>
-      </c>
       <c r="E41" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.35">
@@ -2105,19 +2174,19 @@
         <v>41</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C42" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="D42" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="D42" s="10" t="s">
-        <v>98</v>
-      </c>
       <c r="E42" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.35">
@@ -2126,19 +2195,19 @@
         <v>42</v>
       </c>
       <c r="B43" s="12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C43" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="D43" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="D43" s="12" t="s">
-        <v>100</v>
-      </c>
       <c r="E43" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.35">
@@ -2147,19 +2216,19 @@
         <v>43</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C44" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D44" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="D44" s="12" t="s">
-        <v>102</v>
-      </c>
       <c r="E44" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.35">
@@ -2168,19 +2237,19 @@
         <v>44</v>
       </c>
       <c r="B45" s="12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C45" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="D45" s="12" t="s">
         <v>103</v>
       </c>
-      <c r="D45" s="12" t="s">
-        <v>104</v>
-      </c>
       <c r="E45" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.35">
@@ -2189,19 +2258,19 @@
         <v>45</v>
       </c>
       <c r="B46" s="12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C46" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="D46" s="12" t="s">
         <v>105</v>
       </c>
-      <c r="D46" s="12" t="s">
-        <v>106</v>
-      </c>
       <c r="E46" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.35">
@@ -2210,19 +2279,19 @@
         <v>46</v>
       </c>
       <c r="B47" s="12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C47" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="D47" s="12" t="s">
         <v>107</v>
       </c>
-      <c r="D47" s="12" t="s">
-        <v>108</v>
-      </c>
       <c r="E47" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.35">
@@ -2231,19 +2300,19 @@
         <v>47</v>
       </c>
       <c r="B48" s="13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C48" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="D48" s="13" t="s">
         <v>109</v>
       </c>
-      <c r="D48" s="13" t="s">
-        <v>110</v>
-      </c>
       <c r="E48" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
@@ -2252,19 +2321,19 @@
         <v>48</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C49" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="D49" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="D49" s="13" t="s">
-        <v>112</v>
-      </c>
       <c r="E49" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
@@ -2273,19 +2342,19 @@
         <v>49</v>
       </c>
       <c r="B50" s="13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C50" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="D50" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="D50" s="13" t="s">
-        <v>114</v>
-      </c>
       <c r="E50" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
@@ -2294,19 +2363,19 @@
         <v>50</v>
       </c>
       <c r="B51" s="13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C51" s="13" t="s">
+        <v>114</v>
+      </c>
+      <c r="D51" s="13" t="s">
         <v>115</v>
-      </c>
-      <c r="D51" s="13" t="s">
-        <v>116</v>
       </c>
       <c r="E51" s="11">
         <v>46027</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
@@ -2314,19 +2383,250 @@
         <v>51</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C52" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="D52" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="D52" s="13" t="s">
+      <c r="E52" s="18">
+        <v>46168</v>
+      </c>
+      <c r="F52" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="E52" s="11">
-        <v>46168</v>
-      </c>
-      <c r="F52" s="5" t="s">
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A53" s="2">
+        <v>52</v>
+      </c>
+      <c r="B53" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C53" s="13" t="str">
+        <f>RIGHT(F53,6)</f>
+        <v>GGPDAA</v>
+      </c>
+      <c r="D53" s="13" t="s">
+        <v>187</v>
+      </c>
+      <c r="E53" s="18">
+        <v>46175</v>
+      </c>
+      <c r="F53" s="5" t="s">
         <v>172</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A54" s="2">
+        <v>53</v>
+      </c>
+      <c r="B54" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C54" s="13" t="str">
+        <f t="shared" ref="C54:C63" si="1">RIGHT(F54,6)</f>
+        <v>GGPPAN</v>
+      </c>
+      <c r="D54" s="13" t="s">
+        <v>189</v>
+      </c>
+      <c r="E54" s="18">
+        <v>46175</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A55" s="2">
+        <v>54</v>
+      </c>
+      <c r="B55" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C55" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>GGPJAT</v>
+      </c>
+      <c r="D55" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="E55" s="18">
+        <v>46175</v>
+      </c>
+      <c r="F55" s="5" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A56" s="2">
+        <v>55</v>
+      </c>
+      <c r="B56" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C56" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>GGPPET</v>
+      </c>
+      <c r="D56" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="E56" s="18">
+        <v>46175</v>
+      </c>
+      <c r="F56" s="5" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A57" s="2">
+        <v>56</v>
+      </c>
+      <c r="B57" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C57" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>GGPJOG</v>
+      </c>
+      <c r="D57" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="E57" s="18">
+        <v>46175</v>
+      </c>
+      <c r="F57" s="5" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A58" s="2">
+        <v>57</v>
+      </c>
+      <c r="B58" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C58" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>DPKMAR</v>
+      </c>
+      <c r="D58" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="E58" s="18">
+        <v>46175</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A59" s="2">
+        <v>58</v>
+      </c>
+      <c r="B59" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C59" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>DPKJAS</v>
+      </c>
+      <c r="D59" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="E59" s="18">
+        <v>46175</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A60" s="2">
+        <v>59</v>
+      </c>
+      <c r="B60" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C60" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>DPKSAW</v>
+      </c>
+      <c r="D60" s="13" t="s">
+        <v>185</v>
+      </c>
+      <c r="E60" s="18">
+        <v>46175</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A61" s="2">
+        <v>60</v>
+      </c>
+      <c r="B61" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C61" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>DPKBOJ</v>
+      </c>
+      <c r="D61" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="E61" s="18">
+        <v>46175</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A62" s="2">
+        <v>61</v>
+      </c>
+      <c r="B62" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C62" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>DPKPAR</v>
+      </c>
+      <c r="D62" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="E62" s="18">
+        <v>46175</v>
+      </c>
+      <c r="F62" s="5" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A63" s="2">
+        <v>62</v>
+      </c>
+      <c r="B63" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="C63" s="13" t="str">
+        <f t="shared" si="1"/>
+        <v>DPKLIM</v>
+      </c>
+      <c r="D63" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="E63" s="18">
+        <v>46175</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>182</v>
       </c>
     </row>
   </sheetData>

--- a/Master/KODE DAN RESTO BOM NEW.xlsx
+++ b/Master/KODE DAN RESTO BOM NEW.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\GIS\GIS_ESB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CE6950B-37FB-4887-B490-218E087BFBA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69EC652E-8029-4C40-BE4C-970736C7C521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{2A27DFF0-1BDB-46C7-8D34-C6B2AB0C8283}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="244">
   <si>
     <t>NO</t>
   </si>
@@ -622,6 +622,153 @@
   </si>
   <si>
     <t>START COVER</t>
+  </si>
+  <si>
+    <t>BGRPAD</t>
+  </si>
+  <si>
+    <t>1053.1-G.Bogor - Raya Padjajaran (BGRPAD)</t>
+  </si>
+  <si>
+    <t>BGRTAJ</t>
+  </si>
+  <si>
+    <t>1074.1-G.Bogor - Raya Tajur (BGRTAJ)</t>
+  </si>
+  <si>
+    <t>BGRSAP</t>
+  </si>
+  <si>
+    <t>1079.1-G.Bogor - Saptadji Hadiprawira (BGRSAP)</t>
+  </si>
+  <si>
+    <t>BGRABD</t>
+  </si>
+  <si>
+    <t>1100.1-G.Bogor - R.E. Abdullah (BGRABD)</t>
+  </si>
+  <si>
+    <t>BGRSHO</t>
+  </si>
+  <si>
+    <t>1112.1-G.Bogor - Sholeh Iskandar (BGRSHO)</t>
+  </si>
+  <si>
+    <t>BGRBAT</t>
+  </si>
+  <si>
+    <t>1190.1-G.Bogor - Batu Tulis (BGRBAT)</t>
+  </si>
+  <si>
+    <t>CBITEG</t>
+  </si>
+  <si>
+    <t>1117.1-G.Bogor - Tegar Beriman (CBITEG)</t>
+  </si>
+  <si>
+    <t>CBICIB</t>
+  </si>
+  <si>
+    <t>1128.1-G.Bogor - Raya Cibungbulang (CBICIB)</t>
+  </si>
+  <si>
+    <t>CBIMAY</t>
+  </si>
+  <si>
+    <t>1156.1-G.Bogor - Raya Mayor Oking (CBIMAY)</t>
+  </si>
+  <si>
+    <t>CBICIL</t>
+  </si>
+  <si>
+    <t>1203.1-G.Bogor - Raya Cileungsi (CBICIL)</t>
+  </si>
+  <si>
+    <t>CBIPUN</t>
+  </si>
+  <si>
+    <t>1228.1-G.Bogor - Raya Puncak Gadog (CBIPUN)</t>
+  </si>
+  <si>
+    <t>CBIBOG</t>
+  </si>
+  <si>
+    <t>1245.1-G.Bogor - Raya Bogor (CBIBOG)</t>
+  </si>
+  <si>
+    <t>CBIPAB</t>
+  </si>
+  <si>
+    <t>1249.1-G.Bogor - KP Pabuaran (CBIPAB)</t>
+  </si>
+  <si>
+    <t>CBIKAB</t>
+  </si>
+  <si>
+    <t>1285.1-G.Bogor - KP Kabasiran (CBIKAB)</t>
+  </si>
+  <si>
+    <t>CBIWAR</t>
+  </si>
+  <si>
+    <t>1287.1-G.Bogor - KP Warnasari Barat (CBIWAR)</t>
+  </si>
+  <si>
+    <t>CBIBOJ</t>
+  </si>
+  <si>
+    <t>1344.1-G.Bogor - Bojong Gede (CBIBOJ)</t>
+  </si>
+  <si>
+    <t>BANTEN</t>
+  </si>
+  <si>
+    <t>CPTPUS</t>
+  </si>
+  <si>
+    <t>1081.1-G.Tangsel - Raya Puspitek (CPTPUS)</t>
+  </si>
+  <si>
+    <t>CPTCIA</t>
+  </si>
+  <si>
+    <t>1090.1-G.Tangsel - Ciater Raya (CPTCIA)</t>
+  </si>
+  <si>
+    <t>1117.CBITEG</t>
+  </si>
+  <si>
+    <t>1128.CBICIB</t>
+  </si>
+  <si>
+    <t>1156.CBIMAY</t>
+  </si>
+  <si>
+    <t>1203.CBICIL</t>
+  </si>
+  <si>
+    <t>1228.CBIPUN</t>
+  </si>
+  <si>
+    <t>1245.CBIBOG</t>
+  </si>
+  <si>
+    <t>1249.CBIPAB</t>
+  </si>
+  <si>
+    <t>1285.CBIKAB</t>
+  </si>
+  <si>
+    <t>1287.CBIWAR</t>
+  </si>
+  <si>
+    <t>1344.CBIBOJ</t>
+  </si>
+  <si>
+    <t>1081.CPTPUS</t>
+  </si>
+  <si>
+    <t>1090.CPTCIA</t>
   </si>
 </sst>
 </file>
@@ -683,7 +830,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -738,8 +885,26 @@
         <bgColor rgb="FFF6B26B"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAD1DC"/>
+        <bgColor rgb="FFEAD1DC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB6D7A8"/>
+        <bgColor rgb="FFB6D7A8"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA9999"/>
+        <bgColor rgb="FFEA9999"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -775,12 +940,40 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -830,6 +1023,30 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1299,7 +1516,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0933A7F-4C29-4A64-8B36-B4F9E885B333}">
-  <dimension ref="A1:F63"/>
+  <dimension ref="A1:F81"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="12.08984375" bestFit="1" customWidth="1"/>
@@ -2629,6 +2846,390 @@
         <v>182</v>
       </c>
     </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A64" s="19">
+        <f>1+A61</f>
+        <v>61</v>
+      </c>
+      <c r="B64" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="D64" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="E64" s="21">
+        <v>46059</v>
+      </c>
+      <c r="F64" s="5" t="str">
+        <f>LEFT(D64,4)&amp;"."&amp;LEFT(RIGHT(D64,7),6)</f>
+        <v>1053.BGRPAD</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A65" s="22">
+        <f t="shared" ref="A65:A81" si="2">1+A64</f>
+        <v>62</v>
+      </c>
+      <c r="B65" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="23" t="s">
+        <v>197</v>
+      </c>
+      <c r="D65" s="23" t="s">
+        <v>198</v>
+      </c>
+      <c r="E65" s="24">
+        <v>46059</v>
+      </c>
+      <c r="F65" s="5" t="str">
+        <f t="shared" ref="F65:F81" si="3">LEFT(D65,4)&amp;"."&amp;LEFT(RIGHT(D65,7),6)</f>
+        <v>1074.BGRTAJ</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A66" s="22">
+        <f t="shared" si="2"/>
+        <v>63</v>
+      </c>
+      <c r="B66" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="23" t="s">
+        <v>199</v>
+      </c>
+      <c r="D66" s="23" t="s">
+        <v>200</v>
+      </c>
+      <c r="E66" s="24">
+        <v>46059</v>
+      </c>
+      <c r="F66" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1079.BGRSAP</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A67" s="22">
+        <f t="shared" si="2"/>
+        <v>64</v>
+      </c>
+      <c r="B67" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="23" t="s">
+        <v>201</v>
+      </c>
+      <c r="D67" s="23" t="s">
+        <v>202</v>
+      </c>
+      <c r="E67" s="24">
+        <v>46059</v>
+      </c>
+      <c r="F67" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1100.BGRABD</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A68" s="22">
+        <f t="shared" si="2"/>
+        <v>65</v>
+      </c>
+      <c r="B68" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="23" t="s">
+        <v>203</v>
+      </c>
+      <c r="D68" s="23" t="s">
+        <v>204</v>
+      </c>
+      <c r="E68" s="24">
+        <v>46059</v>
+      </c>
+      <c r="F68" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1112.BGRSHO</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A69" s="22">
+        <f t="shared" si="2"/>
+        <v>66</v>
+      </c>
+      <c r="B69" s="23" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" s="23" t="s">
+        <v>205</v>
+      </c>
+      <c r="D69" s="23" t="s">
+        <v>206</v>
+      </c>
+      <c r="E69" s="24">
+        <v>46059</v>
+      </c>
+      <c r="F69" s="5" t="str">
+        <f t="shared" si="3"/>
+        <v>1190.BGRBAT</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A70" s="22">
+        <f t="shared" si="2"/>
+        <v>67</v>
+      </c>
+      <c r="B70" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="25" t="s">
+        <v>207</v>
+      </c>
+      <c r="D70" s="25" t="s">
+        <v>208</v>
+      </c>
+      <c r="E70" s="24">
+        <v>46059</v>
+      </c>
+      <c r="F70" s="5" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A71" s="22">
+        <f t="shared" si="2"/>
+        <v>68</v>
+      </c>
+      <c r="B71" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" s="25" t="s">
+        <v>209</v>
+      </c>
+      <c r="D71" s="25" t="s">
+        <v>210</v>
+      </c>
+      <c r="E71" s="24">
+        <v>46059</v>
+      </c>
+      <c r="F71" s="5" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A72" s="22">
+        <f t="shared" si="2"/>
+        <v>69</v>
+      </c>
+      <c r="B72" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" s="25" t="s">
+        <v>211</v>
+      </c>
+      <c r="D72" s="25" t="s">
+        <v>212</v>
+      </c>
+      <c r="E72" s="24">
+        <v>46059</v>
+      </c>
+      <c r="F72" s="5" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A73" s="22">
+        <f t="shared" si="2"/>
+        <v>70</v>
+      </c>
+      <c r="B73" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" s="25" t="s">
+        <v>213</v>
+      </c>
+      <c r="D73" s="25" t="s">
+        <v>214</v>
+      </c>
+      <c r="E73" s="24">
+        <v>46059</v>
+      </c>
+      <c r="F73" s="5" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A74" s="22">
+        <f t="shared" si="2"/>
+        <v>71</v>
+      </c>
+      <c r="B74" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" s="25" t="s">
+        <v>215</v>
+      </c>
+      <c r="D74" s="25" t="s">
+        <v>216</v>
+      </c>
+      <c r="E74" s="24">
+        <v>46059</v>
+      </c>
+      <c r="F74" s="5" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A75" s="22">
+        <f t="shared" si="2"/>
+        <v>72</v>
+      </c>
+      <c r="B75" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" s="25" t="s">
+        <v>217</v>
+      </c>
+      <c r="D75" s="25" t="s">
+        <v>218</v>
+      </c>
+      <c r="E75" s="24">
+        <v>46059</v>
+      </c>
+      <c r="F75" s="5" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A76" s="22">
+        <f t="shared" si="2"/>
+        <v>73</v>
+      </c>
+      <c r="B76" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" s="25" t="s">
+        <v>219</v>
+      </c>
+      <c r="D76" s="25" t="s">
+        <v>220</v>
+      </c>
+      <c r="E76" s="24">
+        <v>46059</v>
+      </c>
+      <c r="F76" s="5" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A77" s="22">
+        <f t="shared" si="2"/>
+        <v>74</v>
+      </c>
+      <c r="B77" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C77" s="25" t="s">
+        <v>221</v>
+      </c>
+      <c r="D77" s="25" t="s">
+        <v>222</v>
+      </c>
+      <c r="E77" s="24">
+        <v>46059</v>
+      </c>
+      <c r="F77" s="5" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A78" s="22">
+        <f t="shared" si="2"/>
+        <v>75</v>
+      </c>
+      <c r="B78" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78" s="25" t="s">
+        <v>223</v>
+      </c>
+      <c r="D78" s="25" t="s">
+        <v>224</v>
+      </c>
+      <c r="E78" s="24">
+        <v>46059</v>
+      </c>
+      <c r="F78" s="5" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A79" s="22">
+        <f t="shared" si="2"/>
+        <v>76</v>
+      </c>
+      <c r="B79" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" s="25" t="s">
+        <v>225</v>
+      </c>
+      <c r="D79" s="25" t="s">
+        <v>226</v>
+      </c>
+      <c r="E79" s="24">
+        <v>46059</v>
+      </c>
+      <c r="F79" s="5" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A80" s="22">
+        <f t="shared" si="2"/>
+        <v>77</v>
+      </c>
+      <c r="B80" s="26" t="s">
+        <v>227</v>
+      </c>
+      <c r="C80" s="26" t="s">
+        <v>228</v>
+      </c>
+      <c r="D80" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="E80" s="24">
+        <v>46059</v>
+      </c>
+      <c r="F80" s="5" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A81" s="22">
+        <f t="shared" si="2"/>
+        <v>78</v>
+      </c>
+      <c r="B81" s="26" t="s">
+        <v>227</v>
+      </c>
+      <c r="C81" s="26" t="s">
+        <v>230</v>
+      </c>
+      <c r="D81" s="26" t="s">
+        <v>231</v>
+      </c>
+      <c r="E81" s="24">
+        <v>46059</v>
+      </c>
+      <c r="F81" s="5" t="s">
+        <v>243</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Master/KODE DAN RESTO BOM NEW.xlsx
+++ b/Master/KODE DAN RESTO BOM NEW.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\GIS\GIS_ESB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FORMAT DAN TEMPLATE\T013_Vba_Spit_data\DEX\Master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69EC652E-8029-4C40-BE4C-970736C7C521}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3106CAB-6DCB-4758-91EF-0CBC04A50987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="1" xr2:uid="{2A27DFF0-1BDB-46C7-8D34-C6B2AB0C8283}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{2A27DFF0-1BDB-46C7-8D34-C6B2AB0C8283}"/>
   </bookViews>
   <sheets>
     <sheet name="KODE" sheetId="1" r:id="rId1"/>
@@ -21,23 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="235">
   <si>
     <t>NO</t>
   </si>
@@ -69,18 +58,12 @@
     <t>1060.1-G.Bekasi - M.H. Thamrin (CKRTHA)</t>
   </si>
   <si>
-    <t>17/04/2026</t>
-  </si>
-  <si>
     <t>CKRTAR</t>
   </si>
   <si>
     <t>1129.1-G.Bekasi - Tarum Barat (CKRTAR)</t>
   </si>
   <si>
-    <t>18/04/2026</t>
-  </si>
-  <si>
     <t>CKRMAR</t>
   </si>
   <si>
@@ -93,36 +76,24 @@
     <t>1251.1-G.Bekasi - Sukatani (CKRSUK)</t>
   </si>
   <si>
-    <t>22/04/2026</t>
-  </si>
-  <si>
     <t>CKRHAR</t>
   </si>
   <si>
     <t>1277.1-G.Bekasi - Harapan Indah (CKRHAR)</t>
   </si>
   <si>
-    <t>16/04/2026</t>
-  </si>
-  <si>
     <t>CKRCIK</t>
   </si>
   <si>
     <t>1284.1-G.Bekasi - KP Cikoronjo (CKRCIK)</t>
   </si>
   <si>
-    <t>21/04/2026</t>
-  </si>
-  <si>
     <t>CKRBUL</t>
   </si>
   <si>
     <t>1294.1-G.Bekasi - KP Bulu (CKRBUL)</t>
   </si>
   <si>
-    <t>20/04/2026</t>
-  </si>
-  <si>
     <t>CKRBOS</t>
   </si>
   <si>
@@ -171,9 +142,6 @@
     <t>1059.1-G.Bekasi - Juanda (BKSJUA)</t>
   </si>
   <si>
-    <t>23/04/2026</t>
-  </si>
-  <si>
     <t>BKSJAT</t>
   </si>
   <si>
@@ -291,9 +259,6 @@
     <t>1172.1-G.Jaksel - Ampera Raya (KYBAMP)</t>
   </si>
   <si>
-    <t>30/04/2026</t>
-  </si>
-  <si>
     <t>KYBCIL</t>
   </si>
   <si>
@@ -316,9 +281,6 @@
   </si>
   <si>
     <t>1080.1-G.Jaksel - Kesehatan Raya (KYBKES)</t>
-  </si>
-  <si>
-    <t>29/04/2026</t>
   </si>
   <si>
     <t>KYBLEN</t>
@@ -775,9 +737,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="mm/dd/yyyy"/>
-  </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -973,7 +932,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1003,9 +962,6 @@
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1022,16 +978,10 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1040,15 +990,13 @@
     <xf numFmtId="0" fontId="3" fillId="10" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="11" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1068,9 +1016,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1108,7 +1056,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1214,7 +1162,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1356,7 +1304,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1365,146 +1313,146 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04EABAD4-117C-4DE8-B838-BB6A4F70CD80}">
   <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A1" s="17" t="s">
-        <v>166</v>
-      </c>
-      <c r="B1" s="16" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A2" s="15">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="14">
         <v>550064</v>
       </c>
-      <c r="B2" s="14">
+      <c r="B2" s="13">
         <v>550364</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A3" s="15">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="14">
         <v>550065</v>
       </c>
-      <c r="B3" s="14">
+      <c r="B3" s="13">
         <v>550365</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A4" s="15">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="14">
         <v>550080</v>
       </c>
-      <c r="B4" s="14">
+      <c r="B4" s="13">
         <v>550366</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A5" s="15">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="14">
         <v>550081</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="13">
         <v>550367</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A6" s="15">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="14">
         <v>550260</v>
       </c>
-      <c r="B6" s="14">
+      <c r="B6" s="13">
         <v>550368</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A7" s="15">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="14">
         <v>550261</v>
       </c>
-      <c r="B7" s="14">
+      <c r="B7" s="13">
         <v>550369</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A8" s="15">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="14">
         <v>550262</v>
       </c>
-      <c r="B8" s="14">
+      <c r="B8" s="13">
         <v>550370</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A9" s="15">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="14">
         <v>550263</v>
       </c>
-      <c r="B9" s="14">
+      <c r="B9" s="13">
         <v>550371</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A10" s="15">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="14">
         <v>550264</v>
       </c>
-      <c r="B10" s="14">
+      <c r="B10" s="13">
         <v>550372</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A11" s="15">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="14">
         <v>550265</v>
       </c>
-      <c r="B11" s="14">
+      <c r="B11" s="13">
         <v>550373</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A12" s="15">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="14">
         <v>550266</v>
       </c>
-      <c r="B12" s="14">
+      <c r="B12" s="13">
         <v>550374</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A13" s="15">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="14">
         <v>550267</v>
       </c>
-      <c r="B13" s="14">
+      <c r="B13" s="13">
         <v>550375</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A14" s="15">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="14">
         <v>550268</v>
       </c>
-      <c r="B14" s="14">
+      <c r="B14" s="13">
         <v>550376</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" s="15">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="14">
         <v>550269</v>
       </c>
-      <c r="B15" s="14">
+      <c r="B15" s="13">
         <v>550377</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" s="15">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="14">
         <v>550270</v>
       </c>
-      <c r="B16" s="14">
+      <c r="B16" s="13">
         <v>550378</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" s="15">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="14">
         <v>550271</v>
       </c>
-      <c r="B17" s="14">
+      <c r="B17" s="13">
         <v>550379</v>
       </c>
     </row>
@@ -1516,17 +1464,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0933A7F-4C29-4A64-8B36-B4F9E885B333}">
-  <dimension ref="A1:F81"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:G81"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="41.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="41.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1540,13 +1488,13 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1563,10 +1511,11 @@
         <v>46062</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+        <v>107</v>
+      </c>
+      <c r="G2" s="23"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <f t="shared" ref="A3:A51" si="0">1+A2</f>
         <v>2</v>
@@ -1580,1654 +1529,1690 @@
       <c r="D3" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="4">
+        <v>46129</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="G3" s="23"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="D4" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="4">
+        <v>46130</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="G4" s="23"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="E5" s="4">
+        <v>46130</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>110</v>
+      </c>
+      <c r="G5" s="23"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="4">
+        <v>46134</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>111</v>
+      </c>
+      <c r="G6" s="23"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="2">
+        <f t="shared" si="0"/>
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="4">
+        <v>46128</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="G7" s="23"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="2">
+        <f t="shared" si="0"/>
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="4">
+        <v>46133</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="G8" s="23"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" s="2">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="E9" s="4">
+        <v>46132</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>114</v>
+      </c>
+      <c r="G9" s="23"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="2">
+        <f t="shared" si="0"/>
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="4">
+        <v>46129</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="G10" s="23"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" s="2">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" s="4">
+        <v>46133</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="G11" s="23"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <f t="shared" si="0"/>
+        <v>11</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="4">
+        <v>46129</v>
+      </c>
+      <c r="F12" s="5" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A4" s="2">
-        <f t="shared" si="0"/>
-        <v>3</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="D4" s="6" t="s">
+      <c r="G12" s="23"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" s="2">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="B13" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="E13" s="4">
+        <v>46128</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="G13" s="23"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" s="2">
+        <f t="shared" si="0"/>
         <v>13</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A5" s="2">
-        <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="6" t="s">
+      <c r="B14" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14" s="4">
+        <v>46132</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="G14" s="23"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="2">
+        <f t="shared" si="0"/>
         <v>14</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="B15" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" s="4">
+        <v>46128</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="G15" s="23"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" s="2">
+        <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="E5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A6" s="2">
-        <f t="shared" si="0"/>
-        <v>5</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C6" s="6" t="s">
+      <c r="B16" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="E16" s="4">
+        <v>46128</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="G16" s="23"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" s="2">
+        <f t="shared" si="0"/>
         <v>16</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="B17" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="E17" s="4">
+        <v>46135</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="G17" s="23"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" s="2">
+        <f t="shared" si="0"/>
         <v>17</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="B18" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="4">
+        <v>46133</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="G18" s="23"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A19" s="2">
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A7" s="2">
-        <f t="shared" si="0"/>
-        <v>6</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C7" s="6" t="s">
+      <c r="B19" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="8" t="s">
+        <v>40</v>
+      </c>
+      <c r="D19" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="E19" s="4">
+        <v>46133</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="G19" s="23"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="2">
+        <f t="shared" si="0"/>
         <v>19</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="B20" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C20" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="E20" s="4">
+        <v>46135</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="G20" s="23"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="2">
+        <f t="shared" si="0"/>
         <v>20</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="B21" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E21" s="4">
+        <v>46135</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="G21" s="23"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" s="2">
+        <f t="shared" si="0"/>
         <v>21</v>
       </c>
-      <c r="F7" s="5" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A8" s="2">
-        <f t="shared" si="0"/>
-        <v>7</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C8" s="6" t="s">
+      <c r="B22" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="D22" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E22" s="4">
+        <v>46133</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="G22" s="23"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" s="2">
+        <f t="shared" si="0"/>
         <v>22</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="B23" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="E23" s="4">
+        <v>46133</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="G23" s="23"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" s="2">
+        <f t="shared" si="0"/>
         <v>23</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="B24" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="D24" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="E24" s="4">
+        <v>46133</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="G24" s="23"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" s="2">
+        <f t="shared" si="0"/>
         <v>24</v>
       </c>
-      <c r="F8" s="5" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A9" s="2">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C9" s="6" t="s">
+      <c r="B25" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="E25" s="4">
+        <v>46133</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="G25" s="23"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" s="2">
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="B26" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="D26" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="E26" s="4">
+        <v>46133</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="G26" s="23"/>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A27" s="2">
+        <f t="shared" si="0"/>
         <v>26</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="B27" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="E27" s="4">
+        <v>46133</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="G27" s="23"/>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" s="2">
+        <f t="shared" si="0"/>
         <v>27</v>
       </c>
-      <c r="F9" s="5" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A10" s="2">
-        <f t="shared" si="0"/>
-        <v>9</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C10" s="6" t="s">
+      <c r="B28" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C28" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="D28" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E28" s="4">
+        <v>46135</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="G28" s="23"/>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A29" s="2">
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="B29" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D29" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E29" s="4">
+        <v>46133</v>
+      </c>
+      <c r="F29" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="G29" s="23"/>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A30" s="2">
+        <f t="shared" si="0"/>
         <v>29</v>
       </c>
-      <c r="E10" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A11" s="2">
-        <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="B11" s="6" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" s="6" t="s">
+      <c r="B30" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E30" s="4">
+        <v>46133</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="G30" s="23"/>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A31" s="2">
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="B31" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="E31" s="4">
+        <v>46133</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>136</v>
+      </c>
+      <c r="G31" s="23"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="2">
+        <f t="shared" si="0"/>
         <v>31</v>
       </c>
-      <c r="E11" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A12" s="2">
-        <f t="shared" si="0"/>
-        <v>11</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C12" s="7" t="s">
+      <c r="B32" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E32" s="4">
+        <v>46134</v>
+      </c>
+      <c r="F32" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="G32" s="23"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="2">
+        <f t="shared" si="0"/>
         <v>32</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="B33" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="E33" s="4">
+        <v>46135</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="G33" s="23"/>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A34" s="2">
+        <f t="shared" si="0"/>
         <v>33</v>
       </c>
-      <c r="E12" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A13" s="2">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C13" s="7" t="s">
+      <c r="B34" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="E34" s="4">
+        <v>46134</v>
+      </c>
+      <c r="F34" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="G34" s="23"/>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A35" s="2">
+        <f t="shared" si="0"/>
         <v>34</v>
       </c>
-      <c r="D13" s="7" t="s">
+      <c r="B35" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="C35" s="9" t="s">
+        <v>73</v>
+      </c>
+      <c r="D35" s="9" t="s">
+        <v>74</v>
+      </c>
+      <c r="E35" s="4">
+        <v>46134</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="G35" s="23"/>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="E13" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A14" s="2">
-        <f t="shared" si="0"/>
-        <v>13</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="7" t="s">
+      <c r="B36" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C36" s="10" t="s">
+        <v>75</v>
+      </c>
+      <c r="D36" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="E36" s="4">
+        <v>46142</v>
+      </c>
+      <c r="F36" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="G36" s="23"/>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A37" s="2">
+        <f t="shared" si="0"/>
         <v>36</v>
       </c>
-      <c r="D14" s="7" t="s">
+      <c r="B37" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C37" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D37" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="E37" s="4">
+        <v>46142</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="G37" s="23"/>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="2">
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
-      <c r="E14" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A15" s="2">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="7" t="s">
+      <c r="B38" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C38" s="10" t="s">
+        <v>79</v>
+      </c>
+      <c r="D38" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="E38" s="4">
+        <v>46143</v>
+      </c>
+      <c r="F38" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="G38" s="23"/>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A39" s="2">
+        <f t="shared" si="0"/>
         <v>38</v>
       </c>
-      <c r="D15" s="7" t="s">
+      <c r="B39" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C39" s="10" t="s">
+        <v>81</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="E39" s="4">
+        <v>46142</v>
+      </c>
+      <c r="F39" s="5" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="2">
+        <f t="shared" si="0"/>
         <v>39</v>
       </c>
-      <c r="E15" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F15" s="5" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A16" s="2">
-        <f t="shared" si="0"/>
-        <v>15</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="C16" s="7" t="s">
+      <c r="B40" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C40" s="10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="E40" s="4">
+        <v>46141</v>
+      </c>
+      <c r="F40" s="5" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="2">
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="B41" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C41" s="10" t="s">
+        <v>85</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="E41" s="4">
+        <v>46141</v>
+      </c>
+      <c r="F41" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="2">
+        <f t="shared" si="0"/>
         <v>41</v>
       </c>
-      <c r="E16" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" s="5" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A17" s="2">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="B17" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C17" s="8" t="s">
+      <c r="B42" s="10" t="s">
+        <v>62</v>
+      </c>
+      <c r="C42" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>88</v>
+      </c>
+      <c r="E42" s="4">
+        <v>46141</v>
+      </c>
+      <c r="F42" s="5" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="2">
+        <f t="shared" si="0"/>
         <v>42</v>
       </c>
-      <c r="D17" s="8" t="s">
+      <c r="B43" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C43" s="11" t="s">
+        <v>89</v>
+      </c>
+      <c r="D43" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E43" s="4">
+        <v>46141</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="2">
+        <f t="shared" si="0"/>
         <v>43</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="B44" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C44" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="D44" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="E44" s="4">
+        <v>46141</v>
+      </c>
+      <c r="F44" s="5" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="2">
+        <f t="shared" si="0"/>
         <v>44</v>
       </c>
-      <c r="F17" s="5" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A18" s="2">
-        <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C18" s="8" t="s">
+      <c r="B45" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C45" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="D45" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E45" s="4">
+        <v>46142</v>
+      </c>
+      <c r="F45" s="5" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A46" s="2">
+        <f t="shared" si="0"/>
         <v>45</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="B46" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C46" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="D46" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="E46" s="4">
+        <v>46142</v>
+      </c>
+      <c r="F46" s="5" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="2">
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
-      <c r="E18" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F18" s="5" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A19" s="2">
-        <f t="shared" si="0"/>
-        <v>18</v>
-      </c>
-      <c r="B19" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C19" s="8" t="s">
+      <c r="B47" s="11" t="s">
+        <v>62</v>
+      </c>
+      <c r="C47" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="D47" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="E47" s="4">
+        <v>46141</v>
+      </c>
+      <c r="F47" s="5" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A48" s="2">
+        <f t="shared" si="0"/>
         <v>47</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="B48" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="D48" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="E48" s="4">
+        <v>46142</v>
+      </c>
+      <c r="F48" s="5" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="2">
+        <f t="shared" si="0"/>
         <v>48</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F19" s="5" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A20" s="2">
-        <f t="shared" si="0"/>
-        <v>19</v>
-      </c>
-      <c r="B20" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C20" s="8" t="s">
+      <c r="B49" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C49" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="D49" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="E49" s="4">
+        <v>46142</v>
+      </c>
+      <c r="F49" s="5" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="2">
+        <f t="shared" si="0"/>
         <v>49</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="B50" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C50" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="D50" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="E50" s="4">
+        <v>46142</v>
+      </c>
+      <c r="F50" s="5" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="2">
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F20" s="5" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A21" s="2">
-        <f t="shared" si="0"/>
-        <v>20</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C21" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>52</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A22" s="2">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C22" s="8" t="s">
-        <v>53</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A23" s="2">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="B23" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C23" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F23" s="5" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A24" s="2">
-        <f t="shared" si="0"/>
-        <v>23</v>
-      </c>
-      <c r="B24" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C24" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A25" s="2">
-        <f t="shared" si="0"/>
-        <v>24</v>
-      </c>
-      <c r="B25" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C25" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F25" s="5" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A26" s="2">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C26" s="8" t="s">
-        <v>61</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>62</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F26" s="5" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A27" s="2">
-        <f t="shared" si="0"/>
-        <v>26</v>
-      </c>
-      <c r="B27" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>63</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F27" s="5" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A28" s="2">
-        <f t="shared" si="0"/>
-        <v>27</v>
-      </c>
-      <c r="B28" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C28" s="8" t="s">
-        <v>65</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F28" s="5" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A29" s="2">
-        <f t="shared" si="0"/>
-        <v>28</v>
-      </c>
-      <c r="B29" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C29" s="8" t="s">
-        <v>67</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F29" s="5" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A30" s="2">
-        <f t="shared" si="0"/>
-        <v>29</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C30" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A31" s="2">
-        <f t="shared" si="0"/>
-        <v>30</v>
-      </c>
-      <c r="B31" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C31" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A32" s="2">
-        <f t="shared" si="0"/>
-        <v>31</v>
-      </c>
-      <c r="B32" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>74</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>75</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F32" s="5" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A33" s="2">
-        <f t="shared" si="0"/>
-        <v>32</v>
-      </c>
-      <c r="B33" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>76</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="E33" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="F33" s="5" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A34" s="2">
-        <f t="shared" si="0"/>
-        <v>33</v>
-      </c>
-      <c r="B34" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="E34" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A35" s="2">
-        <f t="shared" si="0"/>
-        <v>34</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="C35" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="E35" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A36" s="2">
-        <f t="shared" si="0"/>
-        <v>35</v>
-      </c>
-      <c r="B36" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C36" s="10" t="s">
-        <v>82</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>83</v>
-      </c>
-      <c r="E36" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F36" s="5" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A37" s="2">
-        <f t="shared" si="0"/>
-        <v>36</v>
-      </c>
-      <c r="B37" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C37" s="10" t="s">
-        <v>85</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>86</v>
-      </c>
-      <c r="E37" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F37" s="5" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A38" s="2">
-        <f t="shared" si="0"/>
-        <v>37</v>
-      </c>
-      <c r="B38" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C38" s="10" t="s">
-        <v>87</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>88</v>
-      </c>
-      <c r="E38" s="11">
-        <v>46027</v>
-      </c>
-      <c r="F38" s="5" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A39" s="2">
-        <f t="shared" si="0"/>
-        <v>38</v>
-      </c>
-      <c r="B39" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C39" s="10" t="s">
-        <v>89</v>
-      </c>
-      <c r="D39" s="10" t="s">
-        <v>90</v>
-      </c>
-      <c r="E39" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F39" s="5" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A40" s="2">
-        <f t="shared" si="0"/>
-        <v>39</v>
-      </c>
-      <c r="B40" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C40" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="D40" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="E40" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F40" s="5" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A41" s="2">
-        <f t="shared" si="0"/>
-        <v>40</v>
-      </c>
-      <c r="B41" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C41" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="D41" s="10" t="s">
-        <v>95</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F41" s="5" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A42" s="2">
-        <f t="shared" si="0"/>
-        <v>41</v>
-      </c>
-      <c r="B42" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="C42" s="10" t="s">
-        <v>96</v>
-      </c>
-      <c r="D42" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="E42" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F42" s="5" t="s">
+      <c r="B51" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C51" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="D51" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="E51" s="4">
+        <v>46143</v>
+      </c>
+      <c r="F51" s="5" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A43" s="2">
-        <f t="shared" si="0"/>
-        <v>42</v>
-      </c>
-      <c r="B43" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="C43" s="12" t="s">
-        <v>98</v>
-      </c>
-      <c r="D43" s="12" t="s">
-        <v>99</v>
-      </c>
-      <c r="E43" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A44" s="2">
-        <f t="shared" si="0"/>
-        <v>43</v>
-      </c>
-      <c r="B44" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="C44" s="12" t="s">
-        <v>100</v>
-      </c>
-      <c r="D44" s="12" t="s">
-        <v>101</v>
-      </c>
-      <c r="E44" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F44" s="5" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A45" s="2">
-        <f t="shared" si="0"/>
-        <v>44</v>
-      </c>
-      <c r="B45" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="C45" s="12" t="s">
-        <v>102</v>
-      </c>
-      <c r="D45" s="12" t="s">
-        <v>103</v>
-      </c>
-      <c r="E45" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F45" s="5" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A46" s="2">
-        <f t="shared" si="0"/>
-        <v>45</v>
-      </c>
-      <c r="B46" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="C46" s="12" t="s">
-        <v>104</v>
-      </c>
-      <c r="D46" s="12" t="s">
-        <v>105</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F46" s="5" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A47" s="2">
-        <f t="shared" si="0"/>
-        <v>46</v>
-      </c>
-      <c r="B47" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="C47" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="D47" s="12" t="s">
-        <v>107</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="F47" s="5" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A48" s="2">
-        <f t="shared" si="0"/>
-        <v>47</v>
-      </c>
-      <c r="B48" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C48" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="D48" s="13" t="s">
-        <v>109</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F48" s="5" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A49" s="2">
-        <f t="shared" si="0"/>
-        <v>48</v>
-      </c>
-      <c r="B49" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C49" s="13" t="s">
-        <v>110</v>
-      </c>
-      <c r="D49" s="13" t="s">
-        <v>111</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F49" s="5" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A50" s="2">
-        <f t="shared" si="0"/>
-        <v>49</v>
-      </c>
-      <c r="B50" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C50" s="13" t="s">
-        <v>112</v>
-      </c>
-      <c r="D50" s="13" t="s">
-        <v>113</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="F50" s="5" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A51" s="2">
-        <f t="shared" si="0"/>
-        <v>50</v>
-      </c>
-      <c r="B51" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C51" s="13" t="s">
-        <v>114</v>
-      </c>
-      <c r="D51" s="13" t="s">
-        <v>115</v>
-      </c>
-      <c r="E51" s="11">
-        <v>46027</v>
-      </c>
-      <c r="F51" s="5" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>51</v>
       </c>
-      <c r="B52" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C52" s="13" t="s">
-        <v>169</v>
-      </c>
-      <c r="D52" s="13" t="s">
-        <v>170</v>
-      </c>
-      <c r="E52" s="18">
+      <c r="B52" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="D52" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="E52" s="4">
         <v>46168</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>52</v>
       </c>
-      <c r="B53" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C53" s="13" t="str">
+      <c r="B53" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C53" s="12" t="str">
         <f>RIGHT(F53,6)</f>
         <v>GGPDAA</v>
       </c>
-      <c r="D53" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="E53" s="18">
-        <v>46175</v>
+      <c r="D53" s="12" t="s">
+        <v>178</v>
+      </c>
+      <c r="E53" s="4">
+        <v>46157</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>53</v>
       </c>
-      <c r="B54" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C54" s="13" t="str">
+      <c r="B54" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C54" s="12" t="str">
         <f t="shared" ref="C54:C63" si="1">RIGHT(F54,6)</f>
         <v>GGPPAN</v>
       </c>
-      <c r="D54" s="13" t="s">
-        <v>189</v>
-      </c>
-      <c r="E54" s="18">
-        <v>46175</v>
+      <c r="D54" s="12" t="s">
+        <v>180</v>
+      </c>
+      <c r="E54" s="4">
+        <v>46157</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>54</v>
       </c>
-      <c r="B55" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C55" s="13" t="str">
+      <c r="B55" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C55" s="12" t="str">
         <f t="shared" si="1"/>
         <v>GGPJAT</v>
       </c>
-      <c r="D55" s="13" t="s">
-        <v>190</v>
-      </c>
-      <c r="E55" s="18">
-        <v>46175</v>
+      <c r="D55" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="E55" s="4">
+        <v>46157</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>55</v>
       </c>
-      <c r="B56" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C56" s="13" t="str">
+      <c r="B56" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C56" s="12" t="str">
         <f t="shared" si="1"/>
         <v>GGPPET</v>
       </c>
-      <c r="D56" s="13" t="s">
-        <v>191</v>
-      </c>
-      <c r="E56" s="18">
-        <v>46175</v>
+      <c r="D56" s="12" t="s">
+        <v>182</v>
+      </c>
+      <c r="E56" s="4">
+        <v>46157</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>56</v>
       </c>
-      <c r="B57" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C57" s="13" t="str">
+      <c r="B57" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C57" s="12" t="str">
         <f t="shared" si="1"/>
         <v>GGPJOG</v>
       </c>
-      <c r="D57" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="E57" s="18">
-        <v>46175</v>
+      <c r="D57" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="E57" s="4">
+        <v>46157</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>57</v>
       </c>
-      <c r="B58" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C58" s="13" t="str">
+      <c r="B58" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C58" s="12" t="str">
         <f t="shared" si="1"/>
         <v>DPKMAR</v>
       </c>
-      <c r="D58" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="E58" s="18">
-        <v>46175</v>
+      <c r="D58" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="E58" s="4">
+        <v>46157</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>58</v>
       </c>
-      <c r="B59" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C59" s="13" t="str">
+      <c r="B59" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C59" s="12" t="str">
         <f t="shared" si="1"/>
         <v>DPKJAS</v>
       </c>
-      <c r="D59" s="13" t="s">
-        <v>184</v>
-      </c>
-      <c r="E59" s="18">
-        <v>46175</v>
+      <c r="D59" s="12" t="s">
+        <v>175</v>
+      </c>
+      <c r="E59" s="4">
+        <v>46157</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>59</v>
       </c>
-      <c r="B60" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C60" s="13" t="str">
+      <c r="B60" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C60" s="12" t="str">
         <f t="shared" si="1"/>
         <v>DPKSAW</v>
       </c>
-      <c r="D60" s="13" t="s">
-        <v>185</v>
-      </c>
-      <c r="E60" s="18">
-        <v>46175</v>
+      <c r="D60" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="E60" s="4">
+        <v>46157</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>60</v>
       </c>
-      <c r="B61" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C61" s="13" t="str">
+      <c r="B61" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C61" s="12" t="str">
         <f t="shared" si="1"/>
         <v>DPKBOJ</v>
       </c>
-      <c r="D61" s="13" t="s">
-        <v>186</v>
-      </c>
-      <c r="E61" s="18">
-        <v>46175</v>
+      <c r="D61" s="12" t="s">
+        <v>177</v>
+      </c>
+      <c r="E61" s="4">
+        <v>46157</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>61</v>
       </c>
-      <c r="B62" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C62" s="13" t="str">
+      <c r="B62" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C62" s="12" t="str">
         <f t="shared" si="1"/>
         <v>DPKPAR</v>
       </c>
-      <c r="D62" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="E62" s="18">
-        <v>46175</v>
+      <c r="D62" s="12" t="s">
+        <v>179</v>
+      </c>
+      <c r="E62" s="4">
+        <v>46157</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>62</v>
       </c>
-      <c r="B63" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C63" s="13" t="str">
+      <c r="B63" s="12" t="s">
+        <v>62</v>
+      </c>
+      <c r="C63" s="12" t="str">
         <f t="shared" si="1"/>
         <v>DPKLIM</v>
       </c>
-      <c r="D63" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="E63" s="18">
-        <v>46175</v>
+      <c r="D63" s="12" t="s">
+        <v>183</v>
+      </c>
+      <c r="E63" s="4">
+        <v>46157</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A64" s="19">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" s="17">
         <f>1+A61</f>
         <v>61</v>
       </c>
-      <c r="B64" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="C64" s="20" t="s">
-        <v>195</v>
-      </c>
-      <c r="D64" s="20" t="s">
-        <v>196</v>
-      </c>
-      <c r="E64" s="21">
-        <v>46059</v>
+      <c r="B64" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C64" s="18" t="s">
+        <v>186</v>
+      </c>
+      <c r="D64" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="E64" s="4">
+        <v>46175</v>
       </c>
       <c r="F64" s="5" t="str">
         <f>LEFT(D64,4)&amp;"."&amp;LEFT(RIGHT(D64,7),6)</f>
         <v>1053.BGRPAD</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A65" s="22">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="19">
         <f t="shared" ref="A65:A81" si="2">1+A64</f>
         <v>62</v>
       </c>
-      <c r="B65" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="C65" s="23" t="s">
-        <v>197</v>
-      </c>
-      <c r="D65" s="23" t="s">
-        <v>198</v>
-      </c>
-      <c r="E65" s="24">
-        <v>46059</v>
+      <c r="B65" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C65" s="20" t="s">
+        <v>188</v>
+      </c>
+      <c r="D65" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="E65" s="4">
+        <v>46175</v>
       </c>
       <c r="F65" s="5" t="str">
-        <f t="shared" ref="F65:F81" si="3">LEFT(D65,4)&amp;"."&amp;LEFT(RIGHT(D65,7),6)</f>
+        <f t="shared" ref="F65:F69" si="3">LEFT(D65,4)&amp;"."&amp;LEFT(RIGHT(D65,7),6)</f>
         <v>1074.BGRTAJ</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A66" s="22">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="19">
         <f t="shared" si="2"/>
         <v>63</v>
       </c>
-      <c r="B66" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="C66" s="23" t="s">
-        <v>199</v>
-      </c>
-      <c r="D66" s="23" t="s">
-        <v>200</v>
-      </c>
-      <c r="E66" s="24">
-        <v>46059</v>
+      <c r="B66" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C66" s="20" t="s">
+        <v>190</v>
+      </c>
+      <c r="D66" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="E66" s="4">
+        <v>46175</v>
       </c>
       <c r="F66" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1079.BGRSAP</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A67" s="22">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="19">
         <f t="shared" si="2"/>
         <v>64</v>
       </c>
-      <c r="B67" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="C67" s="23" t="s">
-        <v>201</v>
-      </c>
-      <c r="D67" s="23" t="s">
-        <v>202</v>
-      </c>
-      <c r="E67" s="24">
-        <v>46059</v>
+      <c r="B67" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C67" s="20" t="s">
+        <v>192</v>
+      </c>
+      <c r="D67" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="E67" s="4">
+        <v>46175</v>
       </c>
       <c r="F67" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1100.BGRABD</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A68" s="22">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="19">
         <f t="shared" si="2"/>
         <v>65</v>
       </c>
-      <c r="B68" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="C68" s="23" t="s">
-        <v>203</v>
-      </c>
-      <c r="D68" s="23" t="s">
-        <v>204</v>
-      </c>
-      <c r="E68" s="24">
-        <v>46059</v>
+      <c r="B68" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C68" s="20" t="s">
+        <v>194</v>
+      </c>
+      <c r="D68" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="E68" s="4">
+        <v>46175</v>
       </c>
       <c r="F68" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1112.BGRSHO</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A69" s="22">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="19">
         <f t="shared" si="2"/>
         <v>66</v>
       </c>
-      <c r="B69" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="C69" s="23" t="s">
-        <v>205</v>
-      </c>
-      <c r="D69" s="23" t="s">
-        <v>206</v>
-      </c>
-      <c r="E69" s="24">
-        <v>46059</v>
+      <c r="B69" s="20" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" s="20" t="s">
+        <v>196</v>
+      </c>
+      <c r="D69" s="20" t="s">
+        <v>197</v>
+      </c>
+      <c r="E69" s="4">
+        <v>46175</v>
       </c>
       <c r="F69" s="5" t="str">
         <f t="shared" si="3"/>
         <v>1190.BGRBAT</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A70" s="22">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="19">
         <f t="shared" si="2"/>
         <v>67</v>
       </c>
-      <c r="B70" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="C70" s="25" t="s">
-        <v>207</v>
-      </c>
-      <c r="D70" s="25" t="s">
-        <v>208</v>
-      </c>
-      <c r="E70" s="24">
-        <v>46059</v>
+      <c r="B70" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="21" t="s">
+        <v>198</v>
+      </c>
+      <c r="D70" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="E70" s="4">
+        <v>46175</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A71" s="22">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="19">
         <f t="shared" si="2"/>
         <v>68</v>
       </c>
-      <c r="B71" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="C71" s="25" t="s">
-        <v>209</v>
-      </c>
-      <c r="D71" s="25" t="s">
-        <v>210</v>
-      </c>
-      <c r="E71" s="24">
-        <v>46059</v>
+      <c r="B71" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" s="21" t="s">
+        <v>200</v>
+      </c>
+      <c r="D71" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="E71" s="4">
+        <v>46175</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A72" s="22">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="19">
         <f t="shared" si="2"/>
         <v>69</v>
       </c>
-      <c r="B72" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="C72" s="25" t="s">
-        <v>211</v>
-      </c>
-      <c r="D72" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="E72" s="24">
-        <v>46059</v>
+      <c r="B72" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" s="21" t="s">
+        <v>202</v>
+      </c>
+      <c r="D72" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="E72" s="4">
+        <v>46175</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A73" s="22">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="19">
         <f t="shared" si="2"/>
         <v>70</v>
       </c>
-      <c r="B73" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="C73" s="25" t="s">
-        <v>213</v>
-      </c>
-      <c r="D73" s="25" t="s">
-        <v>214</v>
-      </c>
-      <c r="E73" s="24">
-        <v>46059</v>
+      <c r="B73" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" s="21" t="s">
+        <v>204</v>
+      </c>
+      <c r="D73" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="E73" s="4">
+        <v>46175</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A74" s="22">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A74" s="19">
         <f t="shared" si="2"/>
         <v>71</v>
       </c>
-      <c r="B74" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="C74" s="25" t="s">
-        <v>215</v>
-      </c>
-      <c r="D74" s="25" t="s">
-        <v>216</v>
-      </c>
-      <c r="E74" s="24">
-        <v>46059</v>
+      <c r="B74" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="D74" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="E74" s="4">
+        <v>46175</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A75" s="22">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A75" s="19">
         <f t="shared" si="2"/>
         <v>72</v>
       </c>
-      <c r="B75" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="C75" s="25" t="s">
-        <v>217</v>
-      </c>
-      <c r="D75" s="25" t="s">
-        <v>218</v>
-      </c>
-      <c r="E75" s="24">
-        <v>46059</v>
+      <c r="B75" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" s="21" t="s">
+        <v>208</v>
+      </c>
+      <c r="D75" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="E75" s="4">
+        <v>46175</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A76" s="22">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A76" s="19">
         <f t="shared" si="2"/>
         <v>73</v>
       </c>
-      <c r="B76" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="C76" s="25" t="s">
-        <v>219</v>
-      </c>
-      <c r="D76" s="25" t="s">
-        <v>220</v>
-      </c>
-      <c r="E76" s="24">
-        <v>46059</v>
+      <c r="B76" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="D76" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="E76" s="4">
+        <v>46175</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A77" s="22">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A77" s="19">
         <f t="shared" si="2"/>
         <v>74</v>
       </c>
-      <c r="B77" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="C77" s="25" t="s">
-        <v>221</v>
-      </c>
-      <c r="D77" s="25" t="s">
-        <v>222</v>
-      </c>
-      <c r="E77" s="24">
-        <v>46059</v>
+      <c r="B77" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C77" s="21" t="s">
+        <v>212</v>
+      </c>
+      <c r="D77" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="E77" s="4">
+        <v>46175</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A78" s="22">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A78" s="19">
         <f t="shared" si="2"/>
         <v>75</v>
       </c>
-      <c r="B78" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="C78" s="25" t="s">
-        <v>223</v>
-      </c>
-      <c r="D78" s="25" t="s">
-        <v>224</v>
-      </c>
-      <c r="E78" s="24">
-        <v>46059</v>
+      <c r="B78" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="D78" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="E78" s="4">
+        <v>46175</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A79" s="22">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A79" s="19">
         <f t="shared" si="2"/>
         <v>76</v>
       </c>
-      <c r="B79" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="C79" s="25" t="s">
-        <v>225</v>
-      </c>
-      <c r="D79" s="25" t="s">
-        <v>226</v>
-      </c>
-      <c r="E79" s="24">
-        <v>46059</v>
+      <c r="B79" s="21" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" s="21" t="s">
+        <v>216</v>
+      </c>
+      <c r="D79" s="21" t="s">
+        <v>217</v>
+      </c>
+      <c r="E79" s="4">
+        <v>46175</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A80" s="22">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A80" s="19">
         <f t="shared" si="2"/>
         <v>77</v>
       </c>
-      <c r="B80" s="26" t="s">
-        <v>227</v>
-      </c>
-      <c r="C80" s="26" t="s">
-        <v>228</v>
-      </c>
-      <c r="D80" s="26" t="s">
-        <v>229</v>
-      </c>
-      <c r="E80" s="24">
-        <v>46059</v>
+      <c r="B80" s="22" t="s">
+        <v>218</v>
+      </c>
+      <c r="C80" s="22" t="s">
+        <v>219</v>
+      </c>
+      <c r="D80" s="22" t="s">
+        <v>220</v>
+      </c>
+      <c r="E80" s="4">
+        <v>46175</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A81" s="22">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A81" s="19">
         <f t="shared" si="2"/>
         <v>78</v>
       </c>
-      <c r="B81" s="26" t="s">
-        <v>227</v>
-      </c>
-      <c r="C81" s="26" t="s">
-        <v>230</v>
-      </c>
-      <c r="D81" s="26" t="s">
-        <v>231</v>
-      </c>
-      <c r="E81" s="24">
-        <v>46059</v>
+      <c r="B81" s="22" t="s">
+        <v>218</v>
+      </c>
+      <c r="C81" s="22" t="s">
+        <v>221</v>
+      </c>
+      <c r="D81" s="22" t="s">
+        <v>222</v>
+      </c>
+      <c r="E81" s="4">
+        <v>46175</v>
       </c>
       <c r="F81" s="5" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
     </row>
   </sheetData>

--- a/Master/KODE DAN RESTO BOM NEW.xlsx
+++ b/Master/KODE DAN RESTO BOM NEW.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FORMAT DAN TEMPLATE\T013_Vba_Spit_data\DEX\Master\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3106CAB-6DCB-4758-91EF-0CBC04A50987}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C679E947-DF82-4B52-A48B-4AFF26AE3E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{2A27DFF0-1BDB-46C7-8D34-C6B2AB0C8283}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{2A27DFF0-1BDB-46C7-8D34-C6B2AB0C8283}"/>
   </bookViews>
   <sheets>
     <sheet name="KODE" sheetId="1" r:id="rId1"/>
@@ -20,6 +20,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -778,7 +789,6 @@
       <sz val="10"/>
       <color rgb="FF333333"/>
       <name val="Roboto"/>
-      <charset val="1"/>
     </font>
     <font>
       <b/>
@@ -1016,9 +1026,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1056,7 +1066,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1162,7 +1172,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1304,7 +1314,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1312,15 +1322,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04EABAD4-117C-4DE8-B838-BB6A4F70CD80}">
-  <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:B22"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="16" t="s">
         <v>157</v>
       </c>
@@ -1328,7 +1338,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="14">
         <v>550064</v>
       </c>
@@ -1336,7 +1346,7 @@
         <v>550364</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="14">
         <v>550065</v>
       </c>
@@ -1344,7 +1354,7 @@
         <v>550365</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="14">
         <v>550080</v>
       </c>
@@ -1352,7 +1362,7 @@
         <v>550366</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="14">
         <v>550081</v>
       </c>
@@ -1360,7 +1370,7 @@
         <v>550367</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="14">
         <v>550260</v>
       </c>
@@ -1368,7 +1378,7 @@
         <v>550368</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="14">
         <v>550261</v>
       </c>
@@ -1376,7 +1386,7 @@
         <v>550369</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="14">
         <v>550262</v>
       </c>
@@ -1384,7 +1394,7 @@
         <v>550370</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="14">
         <v>550263</v>
       </c>
@@ -1392,7 +1402,7 @@
         <v>550371</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="14">
         <v>550264</v>
       </c>
@@ -1400,7 +1410,7 @@
         <v>550372</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="14">
         <v>550265</v>
       </c>
@@ -1408,7 +1418,7 @@
         <v>550373</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="14">
         <v>550266</v>
       </c>
@@ -1416,7 +1426,7 @@
         <v>550374</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="14">
         <v>550267</v>
       </c>
@@ -1424,7 +1434,7 @@
         <v>550375</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="14">
         <v>550268</v>
       </c>
@@ -1432,7 +1442,7 @@
         <v>550376</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="14">
         <v>550269</v>
       </c>
@@ -1440,7 +1450,7 @@
         <v>550377</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="14">
         <v>550270</v>
       </c>
@@ -1448,12 +1458,52 @@
         <v>550378</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="14">
         <v>550271</v>
       </c>
       <c r="B17" s="13">
         <v>550379</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="14">
+        <v>550146</v>
+      </c>
+      <c r="B18" s="13">
+        <v>550430</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="14">
+        <v>550151</v>
+      </c>
+      <c r="B19" s="13">
+        <v>550431</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="14">
+        <v>550152</v>
+      </c>
+      <c r="B20" s="13">
+        <v>550432</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="14">
+        <v>550153</v>
+      </c>
+      <c r="B21" s="13">
+        <v>550433</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="14">
+        <v>550154</v>
+      </c>
+      <c r="B22" s="13">
+        <v>550434</v>
       </c>
     </row>
   </sheetData>
@@ -1465,16 +1515,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0933A7F-4C29-4A64-8B36-B4F9E885B333}">
   <dimension ref="A1:G81"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="41.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="41.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1494,7 +1544,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -1515,7 +1565,7 @@
       </c>
       <c r="G2" s="23"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <f t="shared" ref="A3:A51" si="0">1+A2</f>
         <v>2</v>
@@ -1537,7 +1587,7 @@
       </c>
       <c r="G3" s="23"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -1559,7 +1609,7 @@
       </c>
       <c r="G4" s="23"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -1581,7 +1631,7 @@
       </c>
       <c r="G5" s="23"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -1603,7 +1653,7 @@
       </c>
       <c r="G6" s="23"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -1625,7 +1675,7 @@
       </c>
       <c r="G7" s="23"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -1647,7 +1697,7 @@
       </c>
       <c r="G8" s="23"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -1669,7 +1719,7 @@
       </c>
       <c r="G9" s="23"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -1691,7 +1741,7 @@
       </c>
       <c r="G10" s="23"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -1713,7 +1763,7 @@
       </c>
       <c r="G11" s="23"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -1735,7 +1785,7 @@
       </c>
       <c r="G12" s="23"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -1757,7 +1807,7 @@
       </c>
       <c r="G13" s="23"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -1779,7 +1829,7 @@
       </c>
       <c r="G14" s="23"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -1801,7 +1851,7 @@
       </c>
       <c r="G15" s="23"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -1823,7 +1873,7 @@
       </c>
       <c r="G16" s="23"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -1845,7 +1895,7 @@
       </c>
       <c r="G17" s="23"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -1867,7 +1917,7 @@
       </c>
       <c r="G18" s="23"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -1889,7 +1939,7 @@
       </c>
       <c r="G19" s="23"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -1911,7 +1961,7 @@
       </c>
       <c r="G20" s="23"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -1933,7 +1983,7 @@
       </c>
       <c r="G21" s="23"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -1955,7 +2005,7 @@
       </c>
       <c r="G22" s="23"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -1977,7 +2027,7 @@
       </c>
       <c r="G23" s="23"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -1999,7 +2049,7 @@
       </c>
       <c r="G24" s="23"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -2021,7 +2071,7 @@
       </c>
       <c r="G25" s="23"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -2043,7 +2093,7 @@
       </c>
       <c r="G26" s="23"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -2065,7 +2115,7 @@
       </c>
       <c r="G27" s="23"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -2087,7 +2137,7 @@
       </c>
       <c r="G28" s="23"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -2109,7 +2159,7 @@
       </c>
       <c r="G29" s="23"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -2131,7 +2181,7 @@
       </c>
       <c r="G30" s="23"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -2153,7 +2203,7 @@
       </c>
       <c r="G31" s="23"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -2175,7 +2225,7 @@
       </c>
       <c r="G32" s="23"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -2197,7 +2247,7 @@
       </c>
       <c r="G33" s="23"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -2219,7 +2269,7 @@
       </c>
       <c r="G34" s="23"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -2241,7 +2291,7 @@
       </c>
       <c r="G35" s="23"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -2263,7 +2313,7 @@
       </c>
       <c r="G36" s="23"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -2285,7 +2335,7 @@
       </c>
       <c r="G37" s="23"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -2307,7 +2357,7 @@
       </c>
       <c r="G38" s="23"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -2328,7 +2378,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -2349,7 +2399,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -2370,7 +2420,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -2391,7 +2441,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -2412,7 +2462,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -2433,7 +2483,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -2454,7 +2504,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -2475,7 +2525,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -2496,7 +2546,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -2517,7 +2567,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -2538,7 +2588,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -2559,7 +2609,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -2580,7 +2630,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -2600,7 +2650,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -2621,7 +2671,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -2642,7 +2692,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -2663,7 +2713,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -2684,7 +2734,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -2705,7 +2755,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -2726,7 +2776,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -2747,7 +2797,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -2768,7 +2818,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -2789,7 +2839,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>61</v>
       </c>
@@ -2810,7 +2860,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -2831,7 +2881,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="17">
         <f>1+A61</f>
         <v>61</v>
@@ -2853,7 +2903,7 @@
         <v>1053.BGRPAD</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="19">
         <f t="shared" ref="A65:A81" si="2">1+A64</f>
         <v>62</v>
@@ -2875,7 +2925,7 @@
         <v>1074.BGRTAJ</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="19">
         <f t="shared" si="2"/>
         <v>63</v>
@@ -2897,7 +2947,7 @@
         <v>1079.BGRSAP</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="19">
         <f t="shared" si="2"/>
         <v>64</v>
@@ -2919,7 +2969,7 @@
         <v>1100.BGRABD</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="19">
         <f t="shared" si="2"/>
         <v>65</v>
@@ -2941,7 +2991,7 @@
         <v>1112.BGRSHO</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="19">
         <f t="shared" si="2"/>
         <v>66</v>
@@ -2963,7 +3013,7 @@
         <v>1190.BGRBAT</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="19">
         <f t="shared" si="2"/>
         <v>67</v>
@@ -2984,7 +3034,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="19">
         <f t="shared" si="2"/>
         <v>68</v>
@@ -3005,7 +3055,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="19">
         <f t="shared" si="2"/>
         <v>69</v>
@@ -3026,7 +3076,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="19">
         <f t="shared" si="2"/>
         <v>70</v>
@@ -3047,7 +3097,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" s="19">
         <f t="shared" si="2"/>
         <v>71</v>
@@ -3068,7 +3118,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" s="19">
         <f t="shared" si="2"/>
         <v>72</v>
@@ -3089,7 +3139,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="19">
         <f t="shared" si="2"/>
         <v>73</v>
@@ -3110,7 +3160,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" s="19">
         <f t="shared" si="2"/>
         <v>74</v>
@@ -3131,7 +3181,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" s="19">
         <f t="shared" si="2"/>
         <v>75</v>
@@ -3152,7 +3202,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" s="19">
         <f t="shared" si="2"/>
         <v>76</v>
@@ -3173,7 +3223,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" s="19">
         <f t="shared" si="2"/>
         <v>77</v>
@@ -3194,7 +3244,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" s="19">
         <f t="shared" si="2"/>
         <v>78</v>

--- a/Master/KODE DAN RESTO BOM NEW.xlsx
+++ b/Master/KODE DAN RESTO BOM NEW.xlsx
@@ -5,16 +5,17 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\GIS\GIS_ESB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C679E947-DF82-4B52-A48B-4AFF26AE3E00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD750CFB-C8EE-4932-A17D-9351684A232F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{2A27DFF0-1BDB-46C7-8D34-C6B2AB0C8283}"/>
   </bookViews>
   <sheets>
     <sheet name="KODE" sheetId="1" r:id="rId1"/>
-    <sheet name="RESTO" sheetId="2" r:id="rId2"/>
+    <sheet name="KODE_RESTO" sheetId="3" r:id="rId2"/>
+    <sheet name="RESTO" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="236">
   <si>
     <t>NO</t>
   </si>
@@ -742,6 +743,9 @@
   </si>
   <si>
     <t>1090.CPTCIA</t>
+  </si>
+  <si>
+    <t>1209.MLGSOE</t>
   </si>
 </sst>
 </file>
@@ -942,7 +946,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1007,12 +1011,56 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{7B1D400C-522A-4D8B-AD46-9D4C289835C7}"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="4">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1513,6 +1561,605 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB90F88C-CAFF-4807-B167-4FE3417BBD55}">
+  <dimension ref="A1:D41"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.453125" customWidth="1"/>
+    <col min="3" max="3" width="9.6328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A1" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>157</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B2" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C2" s="24">
+        <v>550004</v>
+      </c>
+      <c r="D2" s="24">
+        <v>550386</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>235</v>
+      </c>
+      <c r="B3" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C3" s="24">
+        <v>550005</v>
+      </c>
+      <c r="D3" s="24">
+        <v>550387</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>235</v>
+      </c>
+      <c r="B4" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C4" s="24">
+        <v>550007</v>
+      </c>
+      <c r="D4" s="24">
+        <v>550388</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>235</v>
+      </c>
+      <c r="B5" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C5" s="24">
+        <v>550009</v>
+      </c>
+      <c r="D5" s="24">
+        <v>550389</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>235</v>
+      </c>
+      <c r="B6" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C6" s="24">
+        <v>550011</v>
+      </c>
+      <c r="D6" s="24">
+        <v>550390</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>235</v>
+      </c>
+      <c r="B7" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C7" s="24">
+        <v>550013</v>
+      </c>
+      <c r="D7" s="24">
+        <v>550391</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>235</v>
+      </c>
+      <c r="B8" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C8" s="24">
+        <v>550043</v>
+      </c>
+      <c r="D8" s="24">
+        <v>550392</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>235</v>
+      </c>
+      <c r="B9" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C9" s="24">
+        <v>550045</v>
+      </c>
+      <c r="D9" s="24">
+        <v>550393</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>235</v>
+      </c>
+      <c r="B10" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C10" s="24">
+        <v>550047</v>
+      </c>
+      <c r="D10" s="24">
+        <v>550394</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>235</v>
+      </c>
+      <c r="B11" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C11" s="24">
+        <v>550049</v>
+      </c>
+      <c r="D11" s="24">
+        <v>550395</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>235</v>
+      </c>
+      <c r="B12" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C12" s="24">
+        <v>550055</v>
+      </c>
+      <c r="D12" s="24">
+        <v>550396</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>235</v>
+      </c>
+      <c r="B13" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C13" s="24">
+        <v>550057</v>
+      </c>
+      <c r="D13" s="24">
+        <v>550397</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A14" t="s">
+        <v>235</v>
+      </c>
+      <c r="B14" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C14" s="24">
+        <v>550059</v>
+      </c>
+      <c r="D14" s="24">
+        <v>550398</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" t="s">
+        <v>235</v>
+      </c>
+      <c r="B15" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C15" s="24">
+        <v>550061</v>
+      </c>
+      <c r="D15" s="24">
+        <v>550399</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" t="s">
+        <v>235</v>
+      </c>
+      <c r="B16" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C16" s="24">
+        <v>550063</v>
+      </c>
+      <c r="D16" s="24">
+        <v>550400</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" t="s">
+        <v>235</v>
+      </c>
+      <c r="B17" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C17" s="24">
+        <v>550077</v>
+      </c>
+      <c r="D17" s="24">
+        <v>550401</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A18" t="s">
+        <v>235</v>
+      </c>
+      <c r="B18" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C18" s="24">
+        <v>550093</v>
+      </c>
+      <c r="D18" s="24">
+        <v>550403</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" t="s">
+        <v>235</v>
+      </c>
+      <c r="B19" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C19" s="24">
+        <v>550101</v>
+      </c>
+      <c r="D19" s="24">
+        <v>550404</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" t="s">
+        <v>235</v>
+      </c>
+      <c r="B20" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C20" s="24">
+        <v>550147</v>
+      </c>
+      <c r="D20" s="24">
+        <v>550405</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" t="s">
+        <v>235</v>
+      </c>
+      <c r="B21" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C21" s="24">
+        <v>550148</v>
+      </c>
+      <c r="D21" s="24">
+        <v>550406</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A22" t="s">
+        <v>235</v>
+      </c>
+      <c r="B22" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C22" s="24">
+        <v>550149</v>
+      </c>
+      <c r="D22" s="24">
+        <v>550407</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A23" t="s">
+        <v>235</v>
+      </c>
+      <c r="B23" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C23" s="24">
+        <v>550150</v>
+      </c>
+      <c r="D23" s="24">
+        <v>550408</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A24" t="s">
+        <v>235</v>
+      </c>
+      <c r="B24" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C24" s="24">
+        <v>550155</v>
+      </c>
+      <c r="D24" s="24">
+        <v>550413</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A25" t="s">
+        <v>235</v>
+      </c>
+      <c r="B25" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C25" s="24">
+        <v>550156</v>
+      </c>
+      <c r="D25" s="24">
+        <v>550414</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A26" t="s">
+        <v>235</v>
+      </c>
+      <c r="B26" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C26" s="24">
+        <v>550157</v>
+      </c>
+      <c r="D26" s="24">
+        <v>550415</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A27" t="s">
+        <v>235</v>
+      </c>
+      <c r="B27" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C27" s="24">
+        <v>550158</v>
+      </c>
+      <c r="D27" s="24">
+        <v>550416</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>235</v>
+      </c>
+      <c r="B28" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C28" s="24">
+        <v>550367</v>
+      </c>
+      <c r="D28" s="24">
+        <v>550423</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>235</v>
+      </c>
+      <c r="B29" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C29" s="24">
+        <v>550369</v>
+      </c>
+      <c r="D29" s="24">
+        <v>550424</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>235</v>
+      </c>
+      <c r="B30" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C30" s="24">
+        <v>550371</v>
+      </c>
+      <c r="D30" s="24">
+        <v>550425</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>235</v>
+      </c>
+      <c r="B31" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C31" s="24">
+        <v>550373</v>
+      </c>
+      <c r="D31" s="24">
+        <v>550426</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>235</v>
+      </c>
+      <c r="B32" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C32" s="24">
+        <v>550375</v>
+      </c>
+      <c r="D32" s="24">
+        <v>550427</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>235</v>
+      </c>
+      <c r="B33" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C33" s="24">
+        <v>550377</v>
+      </c>
+      <c r="D33" s="24">
+        <v>550428</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>235</v>
+      </c>
+      <c r="B34" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C34" s="24">
+        <v>550379</v>
+      </c>
+      <c r="D34" s="24">
+        <v>550429</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>235</v>
+      </c>
+      <c r="B35" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C35" s="24">
+        <v>550151</v>
+      </c>
+      <c r="D35" s="24">
+        <v>550435</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>235</v>
+      </c>
+      <c r="B36" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C36" s="24">
+        <v>550152</v>
+      </c>
+      <c r="D36" s="24">
+        <v>550436</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>235</v>
+      </c>
+      <c r="B37" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C37" s="24">
+        <v>550153</v>
+      </c>
+      <c r="D37" s="24">
+        <v>550437</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>235</v>
+      </c>
+      <c r="B38" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C38" s="24">
+        <v>550154</v>
+      </c>
+      <c r="D38" s="24">
+        <v>550438</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>235</v>
+      </c>
+      <c r="B39" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C39" s="24">
+        <v>550146</v>
+      </c>
+      <c r="D39" s="24">
+        <v>550430</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>235</v>
+      </c>
+      <c r="B40" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C40" s="24">
+        <v>550064</v>
+      </c>
+      <c r="D40" s="24">
+        <v>550364</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>235</v>
+      </c>
+      <c r="B41" s="4">
+        <v>46197</v>
+      </c>
+      <c r="C41" s="24">
+        <v>550065</v>
+      </c>
+      <c r="D41" s="24">
+        <v>550365</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D1:D41">
+    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C1:C1048576">
+    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0933A7F-4C29-4A64-8B36-B4F9E885B333}">
   <dimension ref="A1:G81"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>

--- a/Master/KODE DAN RESTO BOM NEW.xlsx
+++ b/Master/KODE DAN RESTO BOM NEW.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\GIS\GIS_ESB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FORMAT DAN TEMPLATE\T013_Vba_Spit_data\DEX\Master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD750CFB-C8EE-4932-A17D-9351684A232F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80470FC8-DE11-4FD7-8178-C369AFDAA283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{2A27DFF0-1BDB-46C7-8D34-C6B2AB0C8283}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{2A27DFF0-1BDB-46C7-8D34-C6B2AB0C8283}"/>
   </bookViews>
   <sheets>
     <sheet name="KODE" sheetId="1" r:id="rId1"/>
@@ -22,23 +22,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="236">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="239">
   <si>
     <t>NO</t>
   </si>
@@ -746,6 +735,15 @@
   </si>
   <si>
     <t>1209.MLGSOE</t>
+  </si>
+  <si>
+    <t>TGRPEM</t>
+  </si>
+  <si>
+    <t>1376.1-G.Tangerang - Pemda (TGRPEM)</t>
+  </si>
+  <si>
+    <t>1376.TGRPEM</t>
   </si>
 </sst>
 </file>
@@ -803,7 +801,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -873,6 +871,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEA9999"/>
+        <bgColor rgb="FFEA9999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor rgb="FFEA9999"/>
       </patternFill>
     </fill>
@@ -946,7 +950,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1014,22 +1018,15 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{7B1D400C-522A-4D8B-AD46-9D4C289835C7}"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1074,9 +1071,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1114,7 +1111,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1220,7 +1217,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1362,7 +1359,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1371,14 +1368,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04EABAD4-117C-4DE8-B838-BB6A4F70CD80}">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>157</v>
       </c>
@@ -1386,7 +1383,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
         <v>550064</v>
       </c>
@@ -1394,7 +1391,7 @@
         <v>550364</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="14">
         <v>550065</v>
       </c>
@@ -1402,7 +1399,7 @@
         <v>550365</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="14">
         <v>550080</v>
       </c>
@@ -1410,7 +1407,7 @@
         <v>550366</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="14">
         <v>550081</v>
       </c>
@@ -1418,7 +1415,7 @@
         <v>550367</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="14">
         <v>550260</v>
       </c>
@@ -1426,7 +1423,7 @@
         <v>550368</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="14">
         <v>550261</v>
       </c>
@@ -1434,7 +1431,7 @@
         <v>550369</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="14">
         <v>550262</v>
       </c>
@@ -1442,7 +1439,7 @@
         <v>550370</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
         <v>550263</v>
       </c>
@@ -1450,7 +1447,7 @@
         <v>550371</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="14">
         <v>550264</v>
       </c>
@@ -1458,7 +1455,7 @@
         <v>550372</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="14">
         <v>550265</v>
       </c>
@@ -1466,7 +1463,7 @@
         <v>550373</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="14">
         <v>550266</v>
       </c>
@@ -1474,7 +1471,7 @@
         <v>550374</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="14">
         <v>550267</v>
       </c>
@@ -1482,7 +1479,7 @@
         <v>550375</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="14">
         <v>550268</v>
       </c>
@@ -1490,7 +1487,7 @@
         <v>550376</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="14">
         <v>550269</v>
       </c>
@@ -1498,7 +1495,7 @@
         <v>550377</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="14">
         <v>550270</v>
       </c>
@@ -1506,7 +1503,7 @@
         <v>550378</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14">
         <v>550271</v>
       </c>
@@ -1514,7 +1511,7 @@
         <v>550379</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="14">
         <v>550146</v>
       </c>
@@ -1522,7 +1519,7 @@
         <v>550430</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="14">
         <v>550151</v>
       </c>
@@ -1530,7 +1527,7 @@
         <v>550431</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="14">
         <v>550152</v>
       </c>
@@ -1538,7 +1535,7 @@
         <v>550432</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="14">
         <v>550153</v>
       </c>
@@ -1546,7 +1543,7 @@
         <v>550433</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="14">
         <v>550154</v>
       </c>
@@ -1563,15 +1560,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB90F88C-CAFF-4807-B167-4FE3417BBD55}">
   <dimension ref="A1:D41"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.453125" customWidth="1"/>
-    <col min="3" max="3" width="9.6328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.6328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" customWidth="1"/>
+    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>159</v>
       </c>
@@ -1585,7 +1582,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>235</v>
       </c>
@@ -1599,7 +1596,7 @@
         <v>550386</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>235</v>
       </c>
@@ -1613,7 +1610,7 @@
         <v>550387</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>235</v>
       </c>
@@ -1627,7 +1624,7 @@
         <v>550388</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>235</v>
       </c>
@@ -1641,7 +1638,7 @@
         <v>550389</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>235</v>
       </c>
@@ -1655,7 +1652,7 @@
         <v>550390</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>235</v>
       </c>
@@ -1669,7 +1666,7 @@
         <v>550391</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>235</v>
       </c>
@@ -1683,7 +1680,7 @@
         <v>550392</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>235</v>
       </c>
@@ -1697,7 +1694,7 @@
         <v>550393</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>235</v>
       </c>
@@ -1711,7 +1708,7 @@
         <v>550394</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>235</v>
       </c>
@@ -1725,7 +1722,7 @@
         <v>550395</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>235</v>
       </c>
@@ -1739,7 +1736,7 @@
         <v>550396</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>235</v>
       </c>
@@ -1753,7 +1750,7 @@
         <v>550397</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>235</v>
       </c>
@@ -1767,7 +1764,7 @@
         <v>550398</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>235</v>
       </c>
@@ -1781,7 +1778,7 @@
         <v>550399</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>235</v>
       </c>
@@ -1795,7 +1792,7 @@
         <v>550400</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>235</v>
       </c>
@@ -1809,7 +1806,7 @@
         <v>550401</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>235</v>
       </c>
@@ -1823,7 +1820,7 @@
         <v>550403</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>235</v>
       </c>
@@ -1837,7 +1834,7 @@
         <v>550404</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>235</v>
       </c>
@@ -1851,7 +1848,7 @@
         <v>550405</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>235</v>
       </c>
@@ -1865,7 +1862,7 @@
         <v>550406</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>235</v>
       </c>
@@ -1879,7 +1876,7 @@
         <v>550407</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>235</v>
       </c>
@@ -1893,7 +1890,7 @@
         <v>550408</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>235</v>
       </c>
@@ -1907,7 +1904,7 @@
         <v>550413</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>235</v>
       </c>
@@ -1921,7 +1918,7 @@
         <v>550414</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>235</v>
       </c>
@@ -1935,7 +1932,7 @@
         <v>550415</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>235</v>
       </c>
@@ -1949,7 +1946,7 @@
         <v>550416</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>235</v>
       </c>
@@ -1963,7 +1960,7 @@
         <v>550423</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>235</v>
       </c>
@@ -1977,7 +1974,7 @@
         <v>550424</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>235</v>
       </c>
@@ -1991,7 +1988,7 @@
         <v>550425</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>235</v>
       </c>
@@ -2005,7 +2002,7 @@
         <v>550426</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>235</v>
       </c>
@@ -2019,7 +2016,7 @@
         <v>550427</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>235</v>
       </c>
@@ -2033,7 +2030,7 @@
         <v>550428</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>235</v>
       </c>
@@ -2047,7 +2044,7 @@
         <v>550429</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>235</v>
       </c>
@@ -2061,7 +2058,7 @@
         <v>550435</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>235</v>
       </c>
@@ -2075,7 +2072,7 @@
         <v>550436</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>235</v>
       </c>
@@ -2089,7 +2086,7 @@
         <v>550437</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>235</v>
       </c>
@@ -2103,7 +2100,7 @@
         <v>550438</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>235</v>
       </c>
@@ -2117,7 +2114,7 @@
         <v>550430</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>235</v>
       </c>
@@ -2131,7 +2128,7 @@
         <v>550364</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>235</v>
       </c>
@@ -2146,14 +2143,14 @@
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="D1:D41">
-    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
+  <conditionalFormatting sqref="A1:B1">
+    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
     <cfRule type="duplicateValues" dxfId="1" priority="2"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  <conditionalFormatting sqref="D1:D41">
+    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2161,17 +2158,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0933A7F-4C29-4A64-8B36-B4F9E885B333}">
-  <dimension ref="A1:G81"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:G82"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="41.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="41.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2191,7 +2188,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -2212,7 +2209,7 @@
       </c>
       <c r="G2" s="23"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <f t="shared" ref="A3:A51" si="0">1+A2</f>
         <v>2</v>
@@ -2234,7 +2231,7 @@
       </c>
       <c r="G3" s="23"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2256,7 +2253,7 @@
       </c>
       <c r="G4" s="23"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2278,7 +2275,7 @@
       </c>
       <c r="G5" s="23"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2300,7 +2297,7 @@
       </c>
       <c r="G6" s="23"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2322,7 +2319,7 @@
       </c>
       <c r="G7" s="23"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2344,7 +2341,7 @@
       </c>
       <c r="G8" s="23"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2366,7 +2363,7 @@
       </c>
       <c r="G9" s="23"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2388,7 +2385,7 @@
       </c>
       <c r="G10" s="23"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2410,7 +2407,7 @@
       </c>
       <c r="G11" s="23"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2432,7 +2429,7 @@
       </c>
       <c r="G12" s="23"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2454,7 +2451,7 @@
       </c>
       <c r="G13" s="23"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2476,7 +2473,7 @@
       </c>
       <c r="G14" s="23"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2498,7 +2495,7 @@
       </c>
       <c r="G15" s="23"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -2520,7 +2517,7 @@
       </c>
       <c r="G16" s="23"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2542,7 +2539,7 @@
       </c>
       <c r="G17" s="23"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2564,7 +2561,7 @@
       </c>
       <c r="G18" s="23"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -2586,7 +2583,7 @@
       </c>
       <c r="G19" s="23"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2608,7 +2605,7 @@
       </c>
       <c r="G20" s="23"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2630,7 +2627,7 @@
       </c>
       <c r="G21" s="23"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -2652,7 +2649,7 @@
       </c>
       <c r="G22" s="23"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -2674,7 +2671,7 @@
       </c>
       <c r="G23" s="23"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -2696,7 +2693,7 @@
       </c>
       <c r="G24" s="23"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -2718,7 +2715,7 @@
       </c>
       <c r="G25" s="23"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -2740,7 +2737,7 @@
       </c>
       <c r="G26" s="23"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -2762,7 +2759,7 @@
       </c>
       <c r="G27" s="23"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -2784,7 +2781,7 @@
       </c>
       <c r="G28" s="23"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -2806,7 +2803,7 @@
       </c>
       <c r="G29" s="23"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -2828,7 +2825,7 @@
       </c>
       <c r="G30" s="23"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -2850,7 +2847,7 @@
       </c>
       <c r="G31" s="23"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -2872,7 +2869,7 @@
       </c>
       <c r="G32" s="23"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -2894,7 +2891,7 @@
       </c>
       <c r="G33" s="23"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -2916,7 +2913,7 @@
       </c>
       <c r="G34" s="23"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -2938,7 +2935,7 @@
       </c>
       <c r="G35" s="23"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -2960,7 +2957,7 @@
       </c>
       <c r="G36" s="23"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -2982,7 +2979,7 @@
       </c>
       <c r="G37" s="23"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -3004,7 +3001,7 @@
       </c>
       <c r="G38" s="23"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -3025,7 +3022,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -3046,7 +3043,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -3067,7 +3064,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -3088,7 +3085,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -3109,7 +3106,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -3130,7 +3127,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -3151,7 +3148,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -3172,7 +3169,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -3193,7 +3190,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -3214,7 +3211,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -3235,7 +3232,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -3256,7 +3253,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -3277,7 +3274,7 @@
         <v>156</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -3297,7 +3294,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -3318,7 +3315,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -3339,7 +3336,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -3360,7 +3357,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -3381,7 +3378,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -3402,7 +3399,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -3423,7 +3420,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -3444,7 +3441,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -3465,7 +3462,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -3486,7 +3483,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>61</v>
       </c>
@@ -3507,7 +3504,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -3528,7 +3525,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="17">
         <f>1+A61</f>
         <v>61</v>
@@ -3550,9 +3547,9 @@
         <v>1053.BGRPAD</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="19">
-        <f t="shared" ref="A65:A81" si="2">1+A64</f>
+        <f t="shared" ref="A65:A82" si="2">1+A64</f>
         <v>62</v>
       </c>
       <c r="B65" s="20" t="s">
@@ -3572,7 +3569,7 @@
         <v>1074.BGRTAJ</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="19">
         <f t="shared" si="2"/>
         <v>63</v>
@@ -3594,7 +3591,7 @@
         <v>1079.BGRSAP</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="19">
         <f t="shared" si="2"/>
         <v>64</v>
@@ -3616,7 +3613,7 @@
         <v>1100.BGRABD</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="19">
         <f t="shared" si="2"/>
         <v>65</v>
@@ -3638,7 +3635,7 @@
         <v>1112.BGRSHO</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="19">
         <f t="shared" si="2"/>
         <v>66</v>
@@ -3660,7 +3657,7 @@
         <v>1190.BGRBAT</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="19">
         <f t="shared" si="2"/>
         <v>67</v>
@@ -3681,7 +3678,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="19">
         <f t="shared" si="2"/>
         <v>68</v>
@@ -3702,7 +3699,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="19">
         <f t="shared" si="2"/>
         <v>69</v>
@@ -3723,7 +3720,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="19">
         <f t="shared" si="2"/>
         <v>70</v>
@@ -3744,7 +3741,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="19">
         <f t="shared" si="2"/>
         <v>71</v>
@@ -3765,7 +3762,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="19">
         <f t="shared" si="2"/>
         <v>72</v>
@@ -3786,7 +3783,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="19">
         <f t="shared" si="2"/>
         <v>73</v>
@@ -3807,7 +3804,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="19">
         <f t="shared" si="2"/>
         <v>74</v>
@@ -3828,7 +3825,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="19">
         <f t="shared" si="2"/>
         <v>75</v>
@@ -3849,7 +3846,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="19">
         <f t="shared" si="2"/>
         <v>76</v>
@@ -3870,7 +3867,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="19">
         <f t="shared" si="2"/>
         <v>77</v>
@@ -3891,7 +3888,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="19">
         <f t="shared" si="2"/>
         <v>78</v>
@@ -3910,6 +3907,26 @@
       </c>
       <c r="F81" s="5" t="s">
         <v>234</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A82" s="19">
+        <v>79</v>
+      </c>
+      <c r="B82" s="25" t="s">
+        <v>218</v>
+      </c>
+      <c r="C82" s="25" t="s">
+        <v>236</v>
+      </c>
+      <c r="D82" s="25" t="s">
+        <v>237</v>
+      </c>
+      <c r="E82" s="4">
+        <v>46204</v>
+      </c>
+      <c r="F82" s="5" t="s">
+        <v>238</v>
       </c>
     </row>
   </sheetData>

--- a/Master/KODE DAN RESTO BOM NEW.xlsx
+++ b/Master/KODE DAN RESTO BOM NEW.xlsx
@@ -1,33 +1,48 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FORMAT DAN TEMPLATE\T013_Vba_Spit_data\DEX\Master\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80470FC8-DE11-4FD7-8178-C369AFDAA283}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E3D9739-68DB-4D8C-B8C2-769B3936A88B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{2A27DFF0-1BDB-46C7-8D34-C6B2AB0C8283}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{2A27DFF0-1BDB-46C7-8D34-C6B2AB0C8283}"/>
   </bookViews>
   <sheets>
     <sheet name="KODE" sheetId="1" r:id="rId1"/>
     <sheet name="KODE_RESTO" sheetId="3" r:id="rId2"/>
     <sheet name="RESTO" sheetId="2" r:id="rId3"/>
+    <sheet name="EXCLUDE" sheetId="4" r:id="rId4"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">RESTO!$A$1:$F$115</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="359" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="339">
   <si>
     <t>NO</t>
   </si>
@@ -152,9 +167,6 @@
     <t>BKSBIN</t>
   </si>
   <si>
-    <t>101072.1-G.Bekasi - Bintara (BKSBIN)</t>
-  </si>
-  <si>
     <t>BKSGOL</t>
   </si>
   <si>
@@ -744,6 +756,309 @@
   </si>
   <si>
     <t>1376.TGRPEM</t>
+  </si>
+  <si>
+    <t>1072.1-G.Bekasi - Bintara (BKSBIN)</t>
+  </si>
+  <si>
+    <t>CPTALA</t>
+  </si>
+  <si>
+    <t>1130.1-G.Tangsel - Alam Sutera (CPTALA)</t>
+  </si>
+  <si>
+    <t>CPTCIP</t>
+  </si>
+  <si>
+    <t>1138.1-G.Tangsel - Ciputat Jombang (CPTCIP)</t>
+  </si>
+  <si>
+    <t>CPTJUA</t>
+  </si>
+  <si>
+    <t>1146.1-G.Tangsel - Dr Ir H. Juanda (CPTJUA)</t>
+  </si>
+  <si>
+    <t>CPTPON</t>
+  </si>
+  <si>
+    <t>1167.1-G.Tangsel - Pondok Betung Raya (CPTPON)</t>
+  </si>
+  <si>
+    <t>CPTDON</t>
+  </si>
+  <si>
+    <t>1207.1-G.Tangsel - KP Dongkal (CPTDON)</t>
+  </si>
+  <si>
+    <t>CPTSET</t>
+  </si>
+  <si>
+    <t>1219.1-G.Tangsel - Dr Setiabudi (CPTSET)</t>
+  </si>
+  <si>
+    <t>CPTSOE</t>
+  </si>
+  <si>
+    <t>1227.1-G.Tangsel - Kapten Soebijanto (CPTSOE)</t>
+  </si>
+  <si>
+    <t>TNGCIL</t>
+  </si>
+  <si>
+    <t>1063.1-G.Tangerang - Ciledug Raya (TNGCIL)</t>
+  </si>
+  <si>
+    <t>TNGHAS</t>
+  </si>
+  <si>
+    <t>1095.1-G.Tangerang - K.H. Hasyim Ashari (TNGHAS)</t>
+  </si>
+  <si>
+    <t>TNGSAL</t>
+  </si>
+  <si>
+    <t>1139.1-G.Tangerang - Raden Saleh (TNGSAL)</t>
+  </si>
+  <si>
+    <t>TNGMER</t>
+  </si>
+  <si>
+    <t>1186.1-G.Tangerang - Merdeka (TNGMER)</t>
+  </si>
+  <si>
+    <t>TNGHUS</t>
+  </si>
+  <si>
+    <t>1202.1-G.Tangerang - Husein Sastranegara (TNGHUS)</t>
+  </si>
+  <si>
+    <t>TNGPET</t>
+  </si>
+  <si>
+    <t>1282.1-G.Tangerang - DS Petir (TNGPET)</t>
+  </si>
+  <si>
+    <t>TNGKEB</t>
+  </si>
+  <si>
+    <t>1329.1-G.Tangerang - Kebon Cau (TNGKEB)</t>
+  </si>
+  <si>
+    <t>TGRHAR</t>
+  </si>
+  <si>
+    <t>1154.1-G.Tangerang - Harpa Utara (TGRHAR)</t>
+  </si>
+  <si>
+    <t>TGRKUT</t>
+  </si>
+  <si>
+    <t>1177.1-G.Tangerang - Raya Kutabumi (TGRKUT)</t>
+  </si>
+  <si>
+    <t>TGRBIN</t>
+  </si>
+  <si>
+    <t>1220.1-G.Tangerang - Raya Binong (TGRBIN)</t>
+  </si>
+  <si>
+    <t>TGRSIM</t>
+  </si>
+  <si>
+    <t>1223.1-G.Tangerang - Simpang Bitung (TGRSIM)</t>
+  </si>
+  <si>
+    <t>TGRKAM</t>
+  </si>
+  <si>
+    <t>1263.1-G.Tangerang - Raya Kampung Melayu (TGRKAM)</t>
+  </si>
+  <si>
+    <t>TGRGEL</t>
+  </si>
+  <si>
+    <t>1276.1-G.Tangerang - KP Gelam Kulon (TGRGEL)</t>
+  </si>
+  <si>
+    <t>TGRSER</t>
+  </si>
+  <si>
+    <t>1302.1-G.Tangerang - Raya Serang (TGRSER)</t>
+  </si>
+  <si>
+    <t>TGRBAL</t>
+  </si>
+  <si>
+    <t>1326.1-G.Tangerang - Balaraja (TGRBAL)</t>
+  </si>
+  <si>
+    <t>TGRMAU</t>
+  </si>
+  <si>
+    <t>1350.1-G.Tangerang - Raya Mauk (TGRMAU)</t>
+  </si>
+  <si>
+    <t>SRGSUD</t>
+  </si>
+  <si>
+    <t>1217.1-G.Serang - Jend. Sudirman (SRGSUD)</t>
+  </si>
+  <si>
+    <t>SRGSAY</t>
+  </si>
+  <si>
+    <t>1321.1-G.Serang - Kp. Sayabulu (SRGSAY)</t>
+  </si>
+  <si>
+    <t>SRGSER</t>
+  </si>
+  <si>
+    <t>1331.1-G.Serang - Raya Serang Jakarta (SRGSER)</t>
+  </si>
+  <si>
+    <t>SRGPAR</t>
+  </si>
+  <si>
+    <t>1355.1-G.Serang - Parigi (SRGPAR)</t>
+  </si>
+  <si>
+    <t>PDGKAD</t>
+  </si>
+  <si>
+    <t>1295.1-G.Pandeglang - Kadumerak (PDGKAD)</t>
+  </si>
+  <si>
+    <t>RKBPAN</t>
+  </si>
+  <si>
+    <t>1304.1-G.Lebak - Raya Pandeglang (RKBPAN)</t>
+  </si>
+  <si>
+    <t>CLGSER</t>
+  </si>
+  <si>
+    <t>1346.1-G.Cilegon - Raya Serang Cilegon (CLGSER)</t>
+  </si>
+  <si>
+    <t>SBRTUP</t>
+  </si>
+  <si>
+    <t>1187.1-G.Cirebon - Tuparev (SBRTUP)</t>
+  </si>
+  <si>
+    <t>CBNPEM</t>
+  </si>
+  <si>
+    <t>1085.1-G.Cirebon - Pemuda Raya (CBNPEM)</t>
+  </si>
+  <si>
+    <t>KNGARU</t>
+  </si>
+  <si>
+    <t>1283.1-G.Kuningan - Aruji Kartawinata (KNGARU)</t>
+  </si>
+  <si>
+    <t>1130.CPTALA</t>
+  </si>
+  <si>
+    <t>1138.CPTCIP</t>
+  </si>
+  <si>
+    <t>1146.CPTJUA</t>
+  </si>
+  <si>
+    <t>1167.CPTPON</t>
+  </si>
+  <si>
+    <t>1207.CPTDON</t>
+  </si>
+  <si>
+    <t>1219.CPTSET</t>
+  </si>
+  <si>
+    <t>1227.CPTSOE</t>
+  </si>
+  <si>
+    <t>1063.TNGCIL</t>
+  </si>
+  <si>
+    <t>1095.TNGHAS</t>
+  </si>
+  <si>
+    <t>1139.TNGSAL</t>
+  </si>
+  <si>
+    <t>1186.TNGMER</t>
+  </si>
+  <si>
+    <t>1202.TNGHUS</t>
+  </si>
+  <si>
+    <t>1282.TNGPET</t>
+  </si>
+  <si>
+    <t>1329.TNGKEB</t>
+  </si>
+  <si>
+    <t>1154.TGRHAR</t>
+  </si>
+  <si>
+    <t>1177.TGRKUT</t>
+  </si>
+  <si>
+    <t>1220.TGRBIN</t>
+  </si>
+  <si>
+    <t>1223.TGRSIM</t>
+  </si>
+  <si>
+    <t>1263.TGRKAM</t>
+  </si>
+  <si>
+    <t>1276.TGRGEL</t>
+  </si>
+  <si>
+    <t>1302.TGRSER</t>
+  </si>
+  <si>
+    <t>1326.TGRBAL</t>
+  </si>
+  <si>
+    <t>1350.TGRMAU</t>
+  </si>
+  <si>
+    <t>1217.SRGSUD</t>
+  </si>
+  <si>
+    <t>1321.SRGSAY</t>
+  </si>
+  <si>
+    <t>1331.SRGSER</t>
+  </si>
+  <si>
+    <t>1355.SRGPAR</t>
+  </si>
+  <si>
+    <t>1295.PDGKAD</t>
+  </si>
+  <si>
+    <t>1304.RKBPAN</t>
+  </si>
+  <si>
+    <t>1346.CLGSER</t>
+  </si>
+  <si>
+    <t>1187.SBRTUP</t>
+  </si>
+  <si>
+    <t>1085.CBNPEM</t>
+  </si>
+  <si>
+    <t>1283.KNGARU</t>
+  </si>
+  <si>
+    <t>EXCLUDE_DATE</t>
   </si>
 </sst>
 </file>
@@ -801,7 +1116,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="14">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -878,6 +1193,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC000"/>
         <bgColor rgb="FFEA9999"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -1014,19 +1335,39 @@
     <xf numFmtId="0" fontId="3" fillId="12" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Normal 2" xfId="1" xr:uid="{7B1D400C-522A-4D8B-AD46-9D4C289835C7}"/>
   </cellStyles>
-  <dxfs count="3">
+  <dxfs count="5">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1071,9 +1412,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1111,7 +1452,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1217,7 +1558,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1359,7 +1700,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1368,22 +1709,22 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04EABAD4-117C-4DE8-B838-BB6A4F70CD80}">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="B1" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="B1" s="15" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="14">
         <v>550064</v>
       </c>
@@ -1391,7 +1732,7 @@
         <v>550364</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="14">
         <v>550065</v>
       </c>
@@ -1399,7 +1740,7 @@
         <v>550365</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="14">
         <v>550080</v>
       </c>
@@ -1407,7 +1748,7 @@
         <v>550366</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="14">
         <v>550081</v>
       </c>
@@ -1415,7 +1756,7 @@
         <v>550367</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="14">
         <v>550260</v>
       </c>
@@ -1423,7 +1764,7 @@
         <v>550368</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="14">
         <v>550261</v>
       </c>
@@ -1431,7 +1772,7 @@
         <v>550369</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="14">
         <v>550262</v>
       </c>
@@ -1439,7 +1780,7 @@
         <v>550370</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="14">
         <v>550263</v>
       </c>
@@ -1447,7 +1788,7 @@
         <v>550371</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="14">
         <v>550264</v>
       </c>
@@ -1455,7 +1796,7 @@
         <v>550372</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="14">
         <v>550265</v>
       </c>
@@ -1463,7 +1804,7 @@
         <v>550373</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="14">
         <v>550266</v>
       </c>
@@ -1471,7 +1812,7 @@
         <v>550374</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="14">
         <v>550267</v>
       </c>
@@ -1479,7 +1820,7 @@
         <v>550375</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="14">
         <v>550268</v>
       </c>
@@ -1487,7 +1828,7 @@
         <v>550376</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="14">
         <v>550269</v>
       </c>
@@ -1495,7 +1836,7 @@
         <v>550377</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="14">
         <v>550270</v>
       </c>
@@ -1503,7 +1844,7 @@
         <v>550378</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="14">
         <v>550271</v>
       </c>
@@ -1511,7 +1852,7 @@
         <v>550379</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="14">
         <v>550146</v>
       </c>
@@ -1519,7 +1860,7 @@
         <v>550430</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="14">
         <v>550151</v>
       </c>
@@ -1527,7 +1868,7 @@
         <v>550431</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="14">
         <v>550152</v>
       </c>
@@ -1535,7 +1876,7 @@
         <v>550432</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="14">
         <v>550153</v>
       </c>
@@ -1543,7 +1884,7 @@
         <v>550433</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="14">
         <v>550154</v>
       </c>
@@ -1560,597 +1901,597 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB90F88C-CAFF-4807-B167-4FE3417BBD55}">
   <dimension ref="A1:D41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.42578125" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.453125" customWidth="1"/>
+    <col min="3" max="3" width="9.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="16" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="C1" s="16" t="s">
+        <v>156</v>
+      </c>
+      <c r="D1" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="D1" s="15" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B2" s="4">
         <v>46197</v>
       </c>
-      <c r="C2" s="24">
+      <c r="C2" s="23">
         <v>550004</v>
       </c>
-      <c r="D2" s="24">
+      <c r="D2" s="23">
         <v>550386</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B3" s="4">
         <v>46197</v>
       </c>
-      <c r="C3" s="24">
+      <c r="C3" s="23">
         <v>550005</v>
       </c>
-      <c r="D3" s="24">
+      <c r="D3" s="23">
         <v>550387</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B4" s="4">
         <v>46197</v>
       </c>
-      <c r="C4" s="24">
+      <c r="C4" s="23">
         <v>550007</v>
       </c>
-      <c r="D4" s="24">
+      <c r="D4" s="23">
         <v>550388</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B5" s="4">
         <v>46197</v>
       </c>
-      <c r="C5" s="24">
+      <c r="C5" s="23">
         <v>550009</v>
       </c>
-      <c r="D5" s="24">
+      <c r="D5" s="23">
         <v>550389</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B6" s="4">
         <v>46197</v>
       </c>
-      <c r="C6" s="24">
+      <c r="C6" s="23">
         <v>550011</v>
       </c>
-      <c r="D6" s="24">
+      <c r="D6" s="23">
         <v>550390</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B7" s="4">
         <v>46197</v>
       </c>
-      <c r="C7" s="24">
+      <c r="C7" s="23">
         <v>550013</v>
       </c>
-      <c r="D7" s="24">
+      <c r="D7" s="23">
         <v>550391</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B8" s="4">
         <v>46197</v>
       </c>
-      <c r="C8" s="24">
+      <c r="C8" s="23">
         <v>550043</v>
       </c>
-      <c r="D8" s="24">
+      <c r="D8" s="23">
         <v>550392</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B9" s="4">
         <v>46197</v>
       </c>
-      <c r="C9" s="24">
+      <c r="C9" s="23">
         <v>550045</v>
       </c>
-      <c r="D9" s="24">
+      <c r="D9" s="23">
         <v>550393</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B10" s="4">
         <v>46197</v>
       </c>
-      <c r="C10" s="24">
+      <c r="C10" s="23">
         <v>550047</v>
       </c>
-      <c r="D10" s="24">
+      <c r="D10" s="23">
         <v>550394</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B11" s="4">
         <v>46197</v>
       </c>
-      <c r="C11" s="24">
+      <c r="C11" s="23">
         <v>550049</v>
       </c>
-      <c r="D11" s="24">
+      <c r="D11" s="23">
         <v>550395</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B12" s="4">
         <v>46197</v>
       </c>
-      <c r="C12" s="24">
+      <c r="C12" s="23">
         <v>550055</v>
       </c>
-      <c r="D12" s="24">
+      <c r="D12" s="23">
         <v>550396</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B13" s="4">
         <v>46197</v>
       </c>
-      <c r="C13" s="24">
+      <c r="C13" s="23">
         <v>550057</v>
       </c>
-      <c r="D13" s="24">
+      <c r="D13" s="23">
         <v>550397</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B14" s="4">
         <v>46197</v>
       </c>
-      <c r="C14" s="24">
+      <c r="C14" s="23">
         <v>550059</v>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="23">
         <v>550398</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B15" s="4">
         <v>46197</v>
       </c>
-      <c r="C15" s="24">
+      <c r="C15" s="23">
         <v>550061</v>
       </c>
-      <c r="D15" s="24">
+      <c r="D15" s="23">
         <v>550399</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B16" s="4">
         <v>46197</v>
       </c>
-      <c r="C16" s="24">
+      <c r="C16" s="23">
         <v>550063</v>
       </c>
-      <c r="D16" s="24">
+      <c r="D16" s="23">
         <v>550400</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B17" s="4">
         <v>46197</v>
       </c>
-      <c r="C17" s="24">
+      <c r="C17" s="23">
         <v>550077</v>
       </c>
-      <c r="D17" s="24">
+      <c r="D17" s="23">
         <v>550401</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B18" s="4">
         <v>46197</v>
       </c>
-      <c r="C18" s="24">
+      <c r="C18" s="23">
         <v>550093</v>
       </c>
-      <c r="D18" s="24">
+      <c r="D18" s="23">
         <v>550403</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B19" s="4">
         <v>46197</v>
       </c>
-      <c r="C19" s="24">
+      <c r="C19" s="23">
         <v>550101</v>
       </c>
-      <c r="D19" s="24">
+      <c r="D19" s="23">
         <v>550404</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B20" s="4">
         <v>46197</v>
       </c>
-      <c r="C20" s="24">
+      <c r="C20" s="23">
         <v>550147</v>
       </c>
-      <c r="D20" s="24">
+      <c r="D20" s="23">
         <v>550405</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B21" s="4">
         <v>46197</v>
       </c>
-      <c r="C21" s="24">
+      <c r="C21" s="23">
         <v>550148</v>
       </c>
-      <c r="D21" s="24">
+      <c r="D21" s="23">
         <v>550406</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B22" s="4">
         <v>46197</v>
       </c>
-      <c r="C22" s="24">
+      <c r="C22" s="23">
         <v>550149</v>
       </c>
-      <c r="D22" s="24">
+      <c r="D22" s="23">
         <v>550407</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B23" s="4">
         <v>46197</v>
       </c>
-      <c r="C23" s="24">
+      <c r="C23" s="23">
         <v>550150</v>
       </c>
-      <c r="D23" s="24">
+      <c r="D23" s="23">
         <v>550408</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B24" s="4">
         <v>46197</v>
       </c>
-      <c r="C24" s="24">
+      <c r="C24" s="23">
         <v>550155</v>
       </c>
-      <c r="D24" s="24">
+      <c r="D24" s="23">
         <v>550413</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B25" s="4">
         <v>46197</v>
       </c>
-      <c r="C25" s="24">
+      <c r="C25" s="23">
         <v>550156</v>
       </c>
-      <c r="D25" s="24">
+      <c r="D25" s="23">
         <v>550414</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B26" s="4">
         <v>46197</v>
       </c>
-      <c r="C26" s="24">
+      <c r="C26" s="23">
         <v>550157</v>
       </c>
-      <c r="D26" s="24">
+      <c r="D26" s="23">
         <v>550415</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B27" s="4">
         <v>46197</v>
       </c>
-      <c r="C27" s="24">
+      <c r="C27" s="23">
         <v>550158</v>
       </c>
-      <c r="D27" s="24">
+      <c r="D27" s="23">
         <v>550416</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B28" s="4">
         <v>46197</v>
       </c>
-      <c r="C28" s="24">
+      <c r="C28" s="23">
         <v>550367</v>
       </c>
-      <c r="D28" s="24">
+      <c r="D28" s="23">
         <v>550423</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B29" s="4">
         <v>46197</v>
       </c>
-      <c r="C29" s="24">
+      <c r="C29" s="23">
         <v>550369</v>
       </c>
-      <c r="D29" s="24">
+      <c r="D29" s="23">
         <v>550424</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B30" s="4">
         <v>46197</v>
       </c>
-      <c r="C30" s="24">
+      <c r="C30" s="23">
         <v>550371</v>
       </c>
-      <c r="D30" s="24">
+      <c r="D30" s="23">
         <v>550425</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B31" s="4">
         <v>46197</v>
       </c>
-      <c r="C31" s="24">
+      <c r="C31" s="23">
         <v>550373</v>
       </c>
-      <c r="D31" s="24">
+      <c r="D31" s="23">
         <v>550426</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B32" s="4">
         <v>46197</v>
       </c>
-      <c r="C32" s="24">
+      <c r="C32" s="23">
         <v>550375</v>
       </c>
-      <c r="D32" s="24">
+      <c r="D32" s="23">
         <v>550427</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B33" s="4">
         <v>46197</v>
       </c>
-      <c r="C33" s="24">
+      <c r="C33" s="23">
         <v>550377</v>
       </c>
-      <c r="D33" s="24">
+      <c r="D33" s="23">
         <v>550428</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B34" s="4">
         <v>46197</v>
       </c>
-      <c r="C34" s="24">
+      <c r="C34" s="23">
         <v>550379</v>
       </c>
-      <c r="D34" s="24">
+      <c r="D34" s="23">
         <v>550429</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B35" s="4">
         <v>46197</v>
       </c>
-      <c r="C35" s="24">
+      <c r="C35" s="23">
         <v>550151</v>
       </c>
-      <c r="D35" s="24">
+      <c r="D35" s="23">
         <v>550435</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B36" s="4">
         <v>46197</v>
       </c>
-      <c r="C36" s="24">
+      <c r="C36" s="23">
         <v>550152</v>
       </c>
-      <c r="D36" s="24">
+      <c r="D36" s="23">
         <v>550436</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B37" s="4">
         <v>46197</v>
       </c>
-      <c r="C37" s="24">
+      <c r="C37" s="23">
         <v>550153</v>
       </c>
-      <c r="D37" s="24">
+      <c r="D37" s="23">
         <v>550437</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B38" s="4">
         <v>46197</v>
       </c>
-      <c r="C38" s="24">
+      <c r="C38" s="23">
         <v>550154</v>
       </c>
-      <c r="D38" s="24">
+      <c r="D38" s="23">
         <v>550438</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B39" s="4">
         <v>46197</v>
       </c>
-      <c r="C39" s="24">
+      <c r="C39" s="23">
         <v>550146</v>
       </c>
-      <c r="D39" s="24">
+      <c r="D39" s="23">
         <v>550430</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B40" s="4">
         <v>46197</v>
       </c>
-      <c r="C40" s="24">
+      <c r="C40" s="23">
         <v>550064</v>
       </c>
-      <c r="D40" s="24">
+      <c r="D40" s="23">
         <v>550364</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="B41" s="4">
         <v>46197</v>
       </c>
-      <c r="C41" s="24">
+      <c r="C41" s="23">
         <v>550065</v>
       </c>
-      <c r="D41" s="24">
+      <c r="D41" s="23">
         <v>550365</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="2" priority="1"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="C1:C1048576">
-    <cfRule type="duplicateValues" dxfId="1" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:D41">
-    <cfRule type="duplicateValues" dxfId="0" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2158,17 +2499,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0933A7F-4C29-4A64-8B36-B4F9E885B333}">
-  <dimension ref="A1:G82"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F115"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="41.5703125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.54296875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="41.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2182,13 +2523,13 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -2205,11 +2546,10 @@
         <v>46062</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="G2" s="23"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <f t="shared" ref="A3:A51" si="0">1+A2</f>
         <v>2</v>
@@ -2227,11 +2567,10 @@
         <v>46129</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>108</v>
-      </c>
-      <c r="G3" s="23"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2249,11 +2588,10 @@
         <v>46130</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>109</v>
-      </c>
-      <c r="G4" s="23"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2271,11 +2609,10 @@
         <v>46130</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>110</v>
-      </c>
-      <c r="G5" s="23"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2293,11 +2630,10 @@
         <v>46134</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="G6" s="23"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2315,11 +2651,10 @@
         <v>46128</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="G7" s="23"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2337,11 +2672,10 @@
         <v>46133</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="G8" s="23"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2359,11 +2693,10 @@
         <v>46132</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="G9" s="23"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2381,11 +2714,10 @@
         <v>46129</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="G10" s="23"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2403,11 +2735,10 @@
         <v>46133</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="G11" s="23"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2425,11 +2756,10 @@
         <v>46129</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="G12" s="23"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2447,11 +2777,10 @@
         <v>46128</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="G13" s="23"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2469,11 +2798,10 @@
         <v>46132</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="G14" s="23"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2491,11 +2819,10 @@
         <v>46128</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="G15" s="23"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -2513,11 +2840,10 @@
         <v>46128</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="G16" s="23"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2535,11 +2861,10 @@
         <v>46135</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="G17" s="23"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2557,11 +2882,10 @@
         <v>46133</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="G18" s="23"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -2573,17 +2897,16 @@
         <v>40</v>
       </c>
       <c r="D19" s="8" t="s">
-        <v>41</v>
+        <v>238</v>
       </c>
       <c r="E19" s="4">
         <v>46133</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="G19" s="23"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2592,20 +2915,19 @@
         <v>7</v>
       </c>
       <c r="C20" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D20" s="8" t="s">
         <v>42</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>43</v>
       </c>
       <c r="E20" s="4">
         <v>46135</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="G20" s="23"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2614,20 +2936,19 @@
         <v>7</v>
       </c>
       <c r="C21" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D21" s="8" t="s">
         <v>44</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>45</v>
       </c>
       <c r="E21" s="4">
         <v>46135</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="G21" s="23"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -2636,20 +2957,19 @@
         <v>7</v>
       </c>
       <c r="C22" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" s="8" t="s">
         <v>46</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>47</v>
       </c>
       <c r="E22" s="4">
         <v>46133</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="G22" s="23"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -2658,20 +2978,19 @@
         <v>7</v>
       </c>
       <c r="C23" s="8" t="s">
+        <v>47</v>
+      </c>
+      <c r="D23" s="8" t="s">
         <v>48</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>49</v>
       </c>
       <c r="E23" s="4">
         <v>46133</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="G23" s="23"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -2680,20 +2999,19 @@
         <v>7</v>
       </c>
       <c r="C24" s="8" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24" s="8" t="s">
         <v>50</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>51</v>
       </c>
       <c r="E24" s="4">
         <v>46133</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="G24" s="23"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -2702,20 +3020,19 @@
         <v>7</v>
       </c>
       <c r="C25" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="D25" s="8" t="s">
         <v>52</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>53</v>
       </c>
       <c r="E25" s="4">
         <v>46133</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="G25" s="23"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -2724,20 +3041,19 @@
         <v>7</v>
       </c>
       <c r="C26" s="8" t="s">
+        <v>53</v>
+      </c>
+      <c r="D26" s="8" t="s">
         <v>54</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>55</v>
       </c>
       <c r="E26" s="4">
         <v>46133</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>131</v>
-      </c>
-      <c r="G26" s="23"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -2746,20 +3062,19 @@
         <v>7</v>
       </c>
       <c r="C27" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" s="8" t="s">
         <v>56</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>57</v>
       </c>
       <c r="E27" s="4">
         <v>46133</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="G27" s="23"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -2768,20 +3083,19 @@
         <v>7</v>
       </c>
       <c r="C28" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="D28" s="8" t="s">
         <v>58</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>59</v>
       </c>
       <c r="E28" s="4">
         <v>46135</v>
       </c>
       <c r="F28" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="G28" s="23"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -2790,742 +3104,732 @@
         <v>7</v>
       </c>
       <c r="C29" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D29" s="8" t="s">
         <v>60</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>61</v>
       </c>
       <c r="E29" s="4">
         <v>46133</v>
       </c>
       <c r="F29" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="G29" s="23"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <f t="shared" si="0"/>
         <v>29</v>
       </c>
       <c r="B30" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C30" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="C30" s="9" t="s">
+      <c r="D30" s="9" t="s">
         <v>63</v>
-      </c>
-      <c r="D30" s="9" t="s">
-        <v>64</v>
       </c>
       <c r="E30" s="4">
         <v>46133</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="G30" s="23"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C31" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D31" s="9" t="s">
         <v>65</v>
-      </c>
-      <c r="D31" s="9" t="s">
-        <v>66</v>
       </c>
       <c r="E31" s="4">
         <v>46133</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="G31" s="23"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <f t="shared" si="0"/>
         <v>31</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C32" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="D32" s="9" t="s">
         <v>67</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>68</v>
       </c>
       <c r="E32" s="4">
         <v>46134</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="G32" s="23"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <f t="shared" si="0"/>
         <v>32</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C33" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="D33" s="9" t="s">
         <v>69</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>70</v>
       </c>
       <c r="E33" s="4">
         <v>46135</v>
       </c>
       <c r="F33" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="G33" s="23"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <f t="shared" si="0"/>
         <v>33</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C34" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="D34" s="9" t="s">
         <v>71</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>72</v>
       </c>
       <c r="E34" s="4">
         <v>46134</v>
       </c>
       <c r="F34" s="5" t="s">
-        <v>139</v>
-      </c>
-      <c r="G34" s="23"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <f t="shared" si="0"/>
         <v>34</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C35" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="D35" s="9" t="s">
         <v>73</v>
-      </c>
-      <c r="D35" s="9" t="s">
-        <v>74</v>
       </c>
       <c r="E35" s="4">
         <v>46134</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="G35" s="23"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
       <c r="B36" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C36" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="D36" s="10" t="s">
         <v>75</v>
-      </c>
-      <c r="D36" s="10" t="s">
-        <v>76</v>
       </c>
       <c r="E36" s="4">
         <v>46142</v>
       </c>
       <c r="F36" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="G36" s="23"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
       <c r="B37" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C37" s="10" t="s">
+        <v>76</v>
+      </c>
+      <c r="D37" s="10" t="s">
         <v>77</v>
-      </c>
-      <c r="D37" s="10" t="s">
-        <v>78</v>
       </c>
       <c r="E37" s="4">
         <v>46142</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="G37" s="23"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <f t="shared" si="0"/>
         <v>37</v>
       </c>
       <c r="B38" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C38" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="D38" s="10" t="s">
         <v>79</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>80</v>
       </c>
       <c r="E38" s="4">
         <v>46143</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="G38" s="23"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <f t="shared" si="0"/>
         <v>38</v>
       </c>
       <c r="B39" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C39" s="10" t="s">
+        <v>80</v>
+      </c>
+      <c r="D39" s="10" t="s">
         <v>81</v>
-      </c>
-      <c r="D39" s="10" t="s">
-        <v>82</v>
       </c>
       <c r="E39" s="4">
         <v>46142</v>
       </c>
       <c r="F39" s="5" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <f t="shared" si="0"/>
         <v>39</v>
       </c>
       <c r="B40" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C40" s="10" t="s">
+        <v>82</v>
+      </c>
+      <c r="D40" s="10" t="s">
         <v>83</v>
-      </c>
-      <c r="D40" s="10" t="s">
-        <v>84</v>
       </c>
       <c r="E40" s="4">
         <v>46141</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="B41" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C41" s="10" t="s">
+        <v>84</v>
+      </c>
+      <c r="D41" s="10" t="s">
         <v>85</v>
-      </c>
-      <c r="D41" s="10" t="s">
-        <v>86</v>
       </c>
       <c r="E41" s="4">
         <v>46141</v>
       </c>
       <c r="F41" s="5" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <f t="shared" si="0"/>
         <v>41</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C42" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="D42" s="10" t="s">
         <v>87</v>
-      </c>
-      <c r="D42" s="10" t="s">
-        <v>88</v>
       </c>
       <c r="E42" s="4">
         <v>46141</v>
       </c>
       <c r="F42" s="5" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <f t="shared" si="0"/>
         <v>42</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C43" s="11" t="s">
+        <v>88</v>
+      </c>
+      <c r="D43" s="11" t="s">
         <v>89</v>
-      </c>
-      <c r="D43" s="11" t="s">
-        <v>90</v>
       </c>
       <c r="E43" s="4">
         <v>46141</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <f t="shared" si="0"/>
         <v>43</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C44" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="D44" s="11" t="s">
         <v>91</v>
-      </c>
-      <c r="D44" s="11" t="s">
-        <v>92</v>
       </c>
       <c r="E44" s="4">
         <v>46141</v>
       </c>
       <c r="F44" s="5" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <f t="shared" si="0"/>
         <v>44</v>
       </c>
       <c r="B45" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C45" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="D45" s="11" t="s">
         <v>93</v>
-      </c>
-      <c r="D45" s="11" t="s">
-        <v>94</v>
       </c>
       <c r="E45" s="4">
         <v>46142</v>
       </c>
       <c r="F45" s="5" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
       <c r="B46" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C46" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D46" s="11" t="s">
         <v>95</v>
-      </c>
-      <c r="D46" s="11" t="s">
-        <v>96</v>
       </c>
       <c r="E46" s="4">
         <v>46142</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C47" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="D47" s="11" t="s">
         <v>97</v>
-      </c>
-      <c r="D47" s="11" t="s">
-        <v>98</v>
       </c>
       <c r="E47" s="4">
         <v>46141</v>
       </c>
       <c r="F47" s="5" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <f t="shared" si="0"/>
         <v>47</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C48" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="D48" s="12" t="s">
         <v>99</v>
-      </c>
-      <c r="D48" s="12" t="s">
-        <v>100</v>
       </c>
       <c r="E48" s="4">
         <v>46142</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
       <c r="B49" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C49" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="D49" s="12" t="s">
         <v>101</v>
-      </c>
-      <c r="D49" s="12" t="s">
-        <v>102</v>
       </c>
       <c r="E49" s="4">
         <v>46142</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <f t="shared" si="0"/>
         <v>49</v>
       </c>
       <c r="B50" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C50" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="D50" s="12" t="s">
         <v>103</v>
-      </c>
-      <c r="D50" s="12" t="s">
-        <v>104</v>
       </c>
       <c r="E50" s="4">
         <v>46142</v>
       </c>
       <c r="F50" s="5" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
       <c r="B51" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C51" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="D51" s="12" t="s">
         <v>105</v>
-      </c>
-      <c r="D51" s="12" t="s">
-        <v>106</v>
       </c>
       <c r="E51" s="4">
         <v>46143</v>
       </c>
       <c r="F51" s="5" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>51</v>
       </c>
       <c r="B52" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C52" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="D52" s="12" t="s">
         <v>160</v>
-      </c>
-      <c r="D52" s="12" t="s">
-        <v>161</v>
       </c>
       <c r="E52" s="4">
         <v>46168</v>
       </c>
       <c r="F52" s="5" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <v>52</v>
       </c>
       <c r="B53" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C53" s="12" t="str">
         <f>RIGHT(F53,6)</f>
         <v>GGPDAA</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E53" s="4">
         <v>46157</v>
       </c>
       <c r="F53" s="5" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>53</v>
       </c>
       <c r="B54" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C54" s="12" t="str">
         <f t="shared" ref="C54:C63" si="1">RIGHT(F54,6)</f>
         <v>GGPPAN</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="E54" s="4">
         <v>46157</v>
       </c>
       <c r="F54" s="5" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <v>54</v>
       </c>
       <c r="B55" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C55" s="12" t="str">
         <f t="shared" si="1"/>
         <v>GGPJAT</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E55" s="4">
         <v>46157</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>55</v>
       </c>
       <c r="B56" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C56" s="12" t="str">
         <f t="shared" si="1"/>
         <v>GGPPET</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E56" s="4">
         <v>46157</v>
       </c>
       <c r="F56" s="5" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>56</v>
       </c>
       <c r="B57" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C57" s="12" t="str">
         <f t="shared" si="1"/>
         <v>GGPJOG</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E57" s="4">
         <v>46157</v>
       </c>
       <c r="F57" s="5" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>57</v>
       </c>
       <c r="B58" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C58" s="12" t="str">
         <f t="shared" si="1"/>
         <v>DPKMAR</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E58" s="4">
         <v>46157</v>
       </c>
       <c r="F58" s="5" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>58</v>
       </c>
       <c r="B59" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C59" s="12" t="str">
         <f t="shared" si="1"/>
         <v>DPKJAS</v>
       </c>
       <c r="D59" s="12" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="E59" s="4">
         <v>46157</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>59</v>
       </c>
       <c r="B60" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C60" s="12" t="str">
         <f t="shared" si="1"/>
         <v>DPKSAW</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="E60" s="4">
         <v>46157</v>
       </c>
       <c r="F60" s="5" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>60</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C61" s="12" t="str">
         <f t="shared" si="1"/>
         <v>DPKBOJ</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E61" s="4">
         <v>46157</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>61</v>
       </c>
       <c r="B62" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C62" s="12" t="str">
         <f t="shared" si="1"/>
         <v>DPKPAR</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E62" s="4">
         <v>46157</v>
       </c>
       <c r="F62" s="5" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>62</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C63" s="12" t="str">
         <f t="shared" si="1"/>
         <v>DPKLIM</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="E63" s="4">
         <v>46157</v>
       </c>
       <c r="F63" s="5" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="17">
         <f>1+A61</f>
         <v>61</v>
@@ -3534,10 +3838,10 @@
         <v>7</v>
       </c>
       <c r="C64" s="18" t="s">
+        <v>185</v>
+      </c>
+      <c r="D64" s="18" t="s">
         <v>186</v>
-      </c>
-      <c r="D64" s="18" t="s">
-        <v>187</v>
       </c>
       <c r="E64" s="4">
         <v>46175</v>
@@ -3547,19 +3851,19 @@
         <v>1053.BGRPAD</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="19">
-        <f t="shared" ref="A65:A82" si="2">1+A64</f>
+        <f t="shared" ref="A65:A115" si="2">1+A64</f>
         <v>62</v>
       </c>
       <c r="B65" s="20" t="s">
         <v>7</v>
       </c>
       <c r="C65" s="20" t="s">
+        <v>187</v>
+      </c>
+      <c r="D65" s="20" t="s">
         <v>188</v>
-      </c>
-      <c r="D65" s="20" t="s">
-        <v>189</v>
       </c>
       <c r="E65" s="4">
         <v>46175</v>
@@ -3569,7 +3873,7 @@
         <v>1074.BGRTAJ</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="19">
         <f t="shared" si="2"/>
         <v>63</v>
@@ -3578,10 +3882,10 @@
         <v>7</v>
       </c>
       <c r="C66" s="20" t="s">
+        <v>189</v>
+      </c>
+      <c r="D66" s="20" t="s">
         <v>190</v>
-      </c>
-      <c r="D66" s="20" t="s">
-        <v>191</v>
       </c>
       <c r="E66" s="4">
         <v>46175</v>
@@ -3591,7 +3895,7 @@
         <v>1079.BGRSAP</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="19">
         <f t="shared" si="2"/>
         <v>64</v>
@@ -3600,10 +3904,10 @@
         <v>7</v>
       </c>
       <c r="C67" s="20" t="s">
+        <v>191</v>
+      </c>
+      <c r="D67" s="20" t="s">
         <v>192</v>
-      </c>
-      <c r="D67" s="20" t="s">
-        <v>193</v>
       </c>
       <c r="E67" s="4">
         <v>46175</v>
@@ -3613,7 +3917,7 @@
         <v>1100.BGRABD</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="19">
         <f t="shared" si="2"/>
         <v>65</v>
@@ -3622,10 +3926,10 @@
         <v>7</v>
       </c>
       <c r="C68" s="20" t="s">
+        <v>193</v>
+      </c>
+      <c r="D68" s="20" t="s">
         <v>194</v>
-      </c>
-      <c r="D68" s="20" t="s">
-        <v>195</v>
       </c>
       <c r="E68" s="4">
         <v>46175</v>
@@ -3635,7 +3939,7 @@
         <v>1112.BGRSHO</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="19">
         <f t="shared" si="2"/>
         <v>66</v>
@@ -3644,10 +3948,10 @@
         <v>7</v>
       </c>
       <c r="C69" s="20" t="s">
+        <v>195</v>
+      </c>
+      <c r="D69" s="20" t="s">
         <v>196</v>
-      </c>
-      <c r="D69" s="20" t="s">
-        <v>197</v>
       </c>
       <c r="E69" s="4">
         <v>46175</v>
@@ -3657,7 +3961,7 @@
         <v>1190.BGRBAT</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="19">
         <f t="shared" si="2"/>
         <v>67</v>
@@ -3666,19 +3970,19 @@
         <v>7</v>
       </c>
       <c r="C70" s="21" t="s">
+        <v>197</v>
+      </c>
+      <c r="D70" s="21" t="s">
         <v>198</v>
-      </c>
-      <c r="D70" s="21" t="s">
-        <v>199</v>
       </c>
       <c r="E70" s="4">
         <v>46175</v>
       </c>
       <c r="F70" s="5" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="19">
         <f t="shared" si="2"/>
         <v>68</v>
@@ -3687,19 +3991,19 @@
         <v>7</v>
       </c>
       <c r="C71" s="21" t="s">
+        <v>199</v>
+      </c>
+      <c r="D71" s="21" t="s">
         <v>200</v>
-      </c>
-      <c r="D71" s="21" t="s">
-        <v>201</v>
       </c>
       <c r="E71" s="4">
         <v>46175</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="19">
         <f t="shared" si="2"/>
         <v>69</v>
@@ -3708,19 +4012,19 @@
         <v>7</v>
       </c>
       <c r="C72" s="21" t="s">
+        <v>201</v>
+      </c>
+      <c r="D72" s="21" t="s">
         <v>202</v>
-      </c>
-      <c r="D72" s="21" t="s">
-        <v>203</v>
       </c>
       <c r="E72" s="4">
         <v>46175</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="19">
         <f t="shared" si="2"/>
         <v>70</v>
@@ -3729,19 +4033,19 @@
         <v>7</v>
       </c>
       <c r="C73" s="21" t="s">
+        <v>203</v>
+      </c>
+      <c r="D73" s="21" t="s">
         <v>204</v>
-      </c>
-      <c r="D73" s="21" t="s">
-        <v>205</v>
       </c>
       <c r="E73" s="4">
         <v>46175</v>
       </c>
       <c r="F73" s="5" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" s="19">
         <f t="shared" si="2"/>
         <v>71</v>
@@ -3750,19 +4054,19 @@
         <v>7</v>
       </c>
       <c r="C74" s="21" t="s">
+        <v>205</v>
+      </c>
+      <c r="D74" s="21" t="s">
         <v>206</v>
-      </c>
-      <c r="D74" s="21" t="s">
-        <v>207</v>
       </c>
       <c r="E74" s="4">
         <v>46175</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" s="19">
         <f t="shared" si="2"/>
         <v>72</v>
@@ -3771,19 +4075,19 @@
         <v>7</v>
       </c>
       <c r="C75" s="21" t="s">
+        <v>207</v>
+      </c>
+      <c r="D75" s="21" t="s">
         <v>208</v>
-      </c>
-      <c r="D75" s="21" t="s">
-        <v>209</v>
       </c>
       <c r="E75" s="4">
         <v>46175</v>
       </c>
       <c r="F75" s="5" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="19">
         <f t="shared" si="2"/>
         <v>73</v>
@@ -3792,19 +4096,19 @@
         <v>7</v>
       </c>
       <c r="C76" s="21" t="s">
+        <v>209</v>
+      </c>
+      <c r="D76" s="21" t="s">
         <v>210</v>
-      </c>
-      <c r="D76" s="21" t="s">
-        <v>211</v>
       </c>
       <c r="E76" s="4">
         <v>46175</v>
       </c>
       <c r="F76" s="5" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" s="19">
         <f t="shared" si="2"/>
         <v>74</v>
@@ -3813,19 +4117,19 @@
         <v>7</v>
       </c>
       <c r="C77" s="21" t="s">
+        <v>211</v>
+      </c>
+      <c r="D77" s="21" t="s">
         <v>212</v>
-      </c>
-      <c r="D77" s="21" t="s">
-        <v>213</v>
       </c>
       <c r="E77" s="4">
         <v>46175</v>
       </c>
       <c r="F77" s="5" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" s="19">
         <f t="shared" si="2"/>
         <v>75</v>
@@ -3834,19 +4138,19 @@
         <v>7</v>
       </c>
       <c r="C78" s="21" t="s">
+        <v>213</v>
+      </c>
+      <c r="D78" s="21" t="s">
         <v>214</v>
-      </c>
-      <c r="D78" s="21" t="s">
-        <v>215</v>
       </c>
       <c r="E78" s="4">
         <v>46175</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>231</v>
-      </c>
-    </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" s="19">
         <f t="shared" si="2"/>
         <v>76</v>
@@ -3855,78 +4159,1040 @@
         <v>7</v>
       </c>
       <c r="C79" s="21" t="s">
+        <v>215</v>
+      </c>
+      <c r="D79" s="21" t="s">
         <v>216</v>
-      </c>
-      <c r="D79" s="21" t="s">
-        <v>217</v>
       </c>
       <c r="E79" s="4">
         <v>46175</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" s="19">
         <f t="shared" si="2"/>
         <v>77</v>
       </c>
       <c r="B80" s="22" t="s">
+        <v>217</v>
+      </c>
+      <c r="C80" s="22" t="s">
         <v>218</v>
       </c>
-      <c r="C80" s="22" t="s">
+      <c r="D80" s="22" t="s">
         <v>219</v>
-      </c>
-      <c r="D80" s="22" t="s">
-        <v>220</v>
       </c>
       <c r="E80" s="4">
         <v>46175</v>
       </c>
-      <c r="F80" s="5" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F80" s="25" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" s="19">
         <f t="shared" si="2"/>
         <v>78</v>
       </c>
       <c r="B81" s="22" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="C81" s="22" t="s">
+        <v>220</v>
+      </c>
+      <c r="D81" s="22" t="s">
         <v>221</v>
-      </c>
-      <c r="D81" s="22" t="s">
-        <v>222</v>
       </c>
       <c r="E81" s="4">
         <v>46175</v>
       </c>
-      <c r="F81" s="5" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F81" s="25" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" s="19">
         <v>79</v>
       </c>
-      <c r="B82" s="25" t="s">
-        <v>218</v>
-      </c>
-      <c r="C82" s="25" t="s">
+      <c r="B82" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C82" s="24" t="s">
+        <v>235</v>
+      </c>
+      <c r="D82" s="24" t="s">
         <v>236</v>
-      </c>
-      <c r="D82" s="25" t="s">
-        <v>237</v>
       </c>
       <c r="E82" s="4">
         <v>46204</v>
       </c>
-      <c r="F82" s="5" t="s">
-        <v>238</v>
+      <c r="F82" s="25" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A83" s="19">
+        <f t="shared" si="2"/>
+        <v>80</v>
+      </c>
+      <c r="B83" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C83" s="24" t="s">
+        <v>239</v>
+      </c>
+      <c r="D83" s="24" t="s">
+        <v>240</v>
+      </c>
+      <c r="E83" s="4">
+        <v>46212</v>
+      </c>
+      <c r="F83" s="5" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A84" s="19">
+        <f t="shared" si="2"/>
+        <v>81</v>
+      </c>
+      <c r="B84" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C84" s="24" t="s">
+        <v>241</v>
+      </c>
+      <c r="D84" s="24" t="s">
+        <v>242</v>
+      </c>
+      <c r="E84" s="4">
+        <v>46212</v>
+      </c>
+      <c r="F84" s="25" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A85" s="19">
+        <f t="shared" si="2"/>
+        <v>82</v>
+      </c>
+      <c r="B85" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C85" s="24" t="s">
+        <v>243</v>
+      </c>
+      <c r="D85" s="24" t="s">
+        <v>244</v>
+      </c>
+      <c r="E85" s="4">
+        <v>46212</v>
+      </c>
+      <c r="F85" s="25" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A86" s="19">
+        <f t="shared" si="2"/>
+        <v>83</v>
+      </c>
+      <c r="B86" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C86" s="24" t="s">
+        <v>245</v>
+      </c>
+      <c r="D86" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="E86" s="4">
+        <v>46212</v>
+      </c>
+      <c r="F86" s="25" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A87" s="19">
+        <f t="shared" si="2"/>
+        <v>84</v>
+      </c>
+      <c r="B87" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C87" s="24" t="s">
+        <v>247</v>
+      </c>
+      <c r="D87" s="24" t="s">
+        <v>248</v>
+      </c>
+      <c r="E87" s="4">
+        <v>46212</v>
+      </c>
+      <c r="F87" s="25" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A88" s="19">
+        <v>80</v>
+      </c>
+      <c r="B88" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C88" s="24" t="s">
+        <v>249</v>
+      </c>
+      <c r="D88" s="24" t="s">
+        <v>250</v>
+      </c>
+      <c r="E88" s="4">
+        <v>46212</v>
+      </c>
+      <c r="F88" s="25" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A89" s="19">
+        <f t="shared" si="2"/>
+        <v>81</v>
+      </c>
+      <c r="B89" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C89" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="D89" s="24" t="s">
+        <v>252</v>
+      </c>
+      <c r="E89" s="4">
+        <v>46212</v>
+      </c>
+      <c r="F89" s="25" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A90" s="19">
+        <f t="shared" si="2"/>
+        <v>82</v>
+      </c>
+      <c r="B90" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C90" s="24" t="s">
+        <v>253</v>
+      </c>
+      <c r="D90" s="24" t="s">
+        <v>254</v>
+      </c>
+      <c r="E90" s="4">
+        <v>46212</v>
+      </c>
+      <c r="F90" s="25" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A91" s="19">
+        <f t="shared" si="2"/>
+        <v>83</v>
+      </c>
+      <c r="B91" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C91" s="24" t="s">
+        <v>255</v>
+      </c>
+      <c r="D91" s="24" t="s">
+        <v>256</v>
+      </c>
+      <c r="E91" s="4">
+        <v>46212</v>
+      </c>
+      <c r="F91" s="5" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A92" s="19">
+        <f t="shared" si="2"/>
+        <v>84</v>
+      </c>
+      <c r="B92" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C92" s="24" t="s">
+        <v>257</v>
+      </c>
+      <c r="D92" s="24" t="s">
+        <v>258</v>
+      </c>
+      <c r="E92" s="4">
+        <v>46212</v>
+      </c>
+      <c r="F92" s="25" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A93" s="19">
+        <f t="shared" si="2"/>
+        <v>85</v>
+      </c>
+      <c r="B93" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C93" s="24" t="s">
+        <v>259</v>
+      </c>
+      <c r="D93" s="24" t="s">
+        <v>260</v>
+      </c>
+      <c r="E93" s="4">
+        <v>46212</v>
+      </c>
+      <c r="F93" s="25" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A94" s="19">
+        <v>81</v>
+      </c>
+      <c r="B94" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C94" s="24" t="s">
+        <v>261</v>
+      </c>
+      <c r="D94" s="24" t="s">
+        <v>262</v>
+      </c>
+      <c r="E94" s="4">
+        <v>46212</v>
+      </c>
+      <c r="F94" s="25" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A95" s="19">
+        <f t="shared" si="2"/>
+        <v>82</v>
+      </c>
+      <c r="B95" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C95" s="24" t="s">
+        <v>263</v>
+      </c>
+      <c r="D95" s="24" t="s">
+        <v>264</v>
+      </c>
+      <c r="E95" s="4">
+        <v>46212</v>
+      </c>
+      <c r="F95" s="25" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A96" s="19">
+        <f t="shared" si="2"/>
+        <v>83</v>
+      </c>
+      <c r="B96" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C96" s="24" t="s">
+        <v>265</v>
+      </c>
+      <c r="D96" s="24" t="s">
+        <v>266</v>
+      </c>
+      <c r="E96" s="4">
+        <v>46212</v>
+      </c>
+      <c r="F96" s="25" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A97" s="19">
+        <f t="shared" si="2"/>
+        <v>84</v>
+      </c>
+      <c r="B97" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C97" s="24" t="s">
+        <v>267</v>
+      </c>
+      <c r="D97" s="24" t="s">
+        <v>268</v>
+      </c>
+      <c r="E97" s="4">
+        <v>46212</v>
+      </c>
+      <c r="F97" s="25" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A98" s="19">
+        <f t="shared" si="2"/>
+        <v>85</v>
+      </c>
+      <c r="B98" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C98" s="24" t="s">
+        <v>269</v>
+      </c>
+      <c r="D98" s="24" t="s">
+        <v>270</v>
+      </c>
+      <c r="E98" s="4">
+        <v>46212</v>
+      </c>
+      <c r="F98" s="25" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A99" s="19">
+        <f t="shared" si="2"/>
+        <v>86</v>
+      </c>
+      <c r="B99" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C99" s="24" t="s">
+        <v>271</v>
+      </c>
+      <c r="D99" s="24" t="s">
+        <v>272</v>
+      </c>
+      <c r="E99" s="4">
+        <v>46212</v>
+      </c>
+      <c r="F99" s="25" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A100" s="19">
+        <v>82</v>
+      </c>
+      <c r="B100" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C100" s="24" t="s">
+        <v>273</v>
+      </c>
+      <c r="D100" s="24" t="s">
+        <v>274</v>
+      </c>
+      <c r="E100" s="4">
+        <v>46212</v>
+      </c>
+      <c r="F100" s="25" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A101" s="19">
+        <f t="shared" si="2"/>
+        <v>83</v>
+      </c>
+      <c r="B101" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C101" s="24" t="s">
+        <v>275</v>
+      </c>
+      <c r="D101" s="24" t="s">
+        <v>276</v>
+      </c>
+      <c r="E101" s="4">
+        <v>46212</v>
+      </c>
+      <c r="F101" s="25" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A102" s="19">
+        <f t="shared" si="2"/>
+        <v>84</v>
+      </c>
+      <c r="B102" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C102" s="24" t="s">
+        <v>277</v>
+      </c>
+      <c r="D102" s="24" t="s">
+        <v>278</v>
+      </c>
+      <c r="E102" s="4">
+        <v>46212</v>
+      </c>
+      <c r="F102" s="25" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A103" s="19">
+        <f t="shared" si="2"/>
+        <v>85</v>
+      </c>
+      <c r="B103" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C103" s="24" t="s">
+        <v>279</v>
+      </c>
+      <c r="D103" s="24" t="s">
+        <v>280</v>
+      </c>
+      <c r="E103" s="4">
+        <v>46212</v>
+      </c>
+      <c r="F103" s="25" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A104" s="19">
+        <f t="shared" si="2"/>
+        <v>86</v>
+      </c>
+      <c r="B104" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C104" s="24" t="s">
+        <v>281</v>
+      </c>
+      <c r="D104" s="24" t="s">
+        <v>282</v>
+      </c>
+      <c r="E104" s="4">
+        <v>46212</v>
+      </c>
+      <c r="F104" s="25" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A105" s="19">
+        <f t="shared" si="2"/>
+        <v>87</v>
+      </c>
+      <c r="B105" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C105" s="24" t="s">
+        <v>283</v>
+      </c>
+      <c r="D105" s="24" t="s">
+        <v>284</v>
+      </c>
+      <c r="E105" s="4">
+        <v>46212</v>
+      </c>
+      <c r="F105" s="25" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A106" s="19">
+        <v>83</v>
+      </c>
+      <c r="B106" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C106" s="24" t="s">
+        <v>285</v>
+      </c>
+      <c r="D106" s="24" t="s">
+        <v>286</v>
+      </c>
+      <c r="E106" s="4">
+        <v>46212</v>
+      </c>
+      <c r="F106" s="25" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A107" s="19">
+        <f t="shared" si="2"/>
+        <v>84</v>
+      </c>
+      <c r="B107" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C107" s="24" t="s">
+        <v>287</v>
+      </c>
+      <c r="D107" s="24" t="s">
+        <v>288</v>
+      </c>
+      <c r="E107" s="4">
+        <v>46212</v>
+      </c>
+      <c r="F107" s="25" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A108" s="19">
+        <f t="shared" si="2"/>
+        <v>85</v>
+      </c>
+      <c r="B108" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C108" s="24" t="s">
+        <v>289</v>
+      </c>
+      <c r="D108" s="24" t="s">
+        <v>290</v>
+      </c>
+      <c r="E108" s="4">
+        <v>46212</v>
+      </c>
+      <c r="F108" s="25" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A109" s="19">
+        <f t="shared" si="2"/>
+        <v>86</v>
+      </c>
+      <c r="B109" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C109" s="24" t="s">
+        <v>291</v>
+      </c>
+      <c r="D109" s="24" t="s">
+        <v>292</v>
+      </c>
+      <c r="E109" s="4">
+        <v>46212</v>
+      </c>
+      <c r="F109" s="25" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A110" s="19">
+        <f t="shared" si="2"/>
+        <v>87</v>
+      </c>
+      <c r="B110" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C110" s="24" t="s">
+        <v>293</v>
+      </c>
+      <c r="D110" s="24" t="s">
+        <v>294</v>
+      </c>
+      <c r="E110" s="4">
+        <v>46212</v>
+      </c>
+      <c r="F110" s="25" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A111" s="19">
+        <f t="shared" si="2"/>
+        <v>88</v>
+      </c>
+      <c r="B111" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C111" s="24" t="s">
+        <v>295</v>
+      </c>
+      <c r="D111" s="24" t="s">
+        <v>296</v>
+      </c>
+      <c r="E111" s="4">
+        <v>46212</v>
+      </c>
+      <c r="F111" s="25" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A112" s="19">
+        <v>84</v>
+      </c>
+      <c r="B112" s="24" t="s">
+        <v>217</v>
+      </c>
+      <c r="C112" s="24" t="s">
+        <v>297</v>
+      </c>
+      <c r="D112" s="24" t="s">
+        <v>298</v>
+      </c>
+      <c r="E112" s="4">
+        <v>46212</v>
+      </c>
+      <c r="F112" s="25" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A113" s="19">
+        <f t="shared" si="2"/>
+        <v>85</v>
+      </c>
+      <c r="B113" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="C113" s="24" t="s">
+        <v>299</v>
+      </c>
+      <c r="D113" s="24" t="s">
+        <v>300</v>
+      </c>
+      <c r="E113" s="4">
+        <v>46212</v>
+      </c>
+      <c r="F113" s="5" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A114" s="19">
+        <f t="shared" si="2"/>
+        <v>86</v>
+      </c>
+      <c r="B114" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="C114" s="24" t="s">
+        <v>301</v>
+      </c>
+      <c r="D114" s="24" t="s">
+        <v>302</v>
+      </c>
+      <c r="E114" s="4">
+        <v>46212</v>
+      </c>
+      <c r="F114" s="5" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A115" s="19">
+        <f t="shared" si="2"/>
+        <v>87</v>
+      </c>
+      <c r="B115" s="24" t="s">
+        <v>4</v>
+      </c>
+      <c r="C115" s="24" t="s">
+        <v>303</v>
+      </c>
+      <c r="D115" s="24" t="s">
+        <v>304</v>
+      </c>
+      <c r="E115" s="4">
+        <v>46212</v>
+      </c>
+      <c r="F115" s="5" t="s">
+        <v>337</v>
+      </c>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="D83:D115">
+    <cfRule type="duplicateValues" dxfId="1" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{620FB88A-C9C3-47FD-BB4D-39DF868892A8}">
+  <dimension ref="A1:B32"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A2" s="25" t="s">
+        <v>232</v>
+      </c>
+      <c r="B2" s="4">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A3" s="25" t="s">
+        <v>233</v>
+      </c>
+      <c r="B3" s="4">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A4" s="25" t="s">
+        <v>237</v>
+      </c>
+      <c r="B4" s="4">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A5" s="25" t="s">
+        <v>306</v>
+      </c>
+      <c r="B5" s="4">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="25" t="s">
+        <v>307</v>
+      </c>
+      <c r="B6" s="4">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" s="25" t="s">
+        <v>308</v>
+      </c>
+      <c r="B7" s="4">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="25" t="s">
+        <v>309</v>
+      </c>
+      <c r="B8" s="4">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" s="25" t="s">
+        <v>310</v>
+      </c>
+      <c r="B9" s="4">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A10" s="25" t="s">
+        <v>311</v>
+      </c>
+      <c r="B10" s="4">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" s="25" t="s">
+        <v>312</v>
+      </c>
+      <c r="B11" s="4">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A12" s="25" t="s">
+        <v>314</v>
+      </c>
+      <c r="B12" s="4">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A13" s="25" t="s">
+        <v>315</v>
+      </c>
+      <c r="B13" s="4">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A14" s="25" t="s">
+        <v>316</v>
+      </c>
+      <c r="B14" s="4">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A15" s="25" t="s">
+        <v>317</v>
+      </c>
+      <c r="B15" s="4">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A16" s="25" t="s">
+        <v>318</v>
+      </c>
+      <c r="B16" s="4">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A17" s="25" t="s">
+        <v>319</v>
+      </c>
+      <c r="B17" s="4">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A18" s="25" t="s">
+        <v>320</v>
+      </c>
+      <c r="B18" s="4">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A19" s="25" t="s">
+        <v>321</v>
+      </c>
+      <c r="B19" s="4">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A20" s="25" t="s">
+        <v>322</v>
+      </c>
+      <c r="B20" s="4">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A21" s="25" t="s">
+        <v>323</v>
+      </c>
+      <c r="B21" s="4">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A22" s="25" t="s">
+        <v>324</v>
+      </c>
+      <c r="B22" s="4">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A23" s="25" t="s">
+        <v>325</v>
+      </c>
+      <c r="B23" s="4">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A24" s="25" t="s">
+        <v>326</v>
+      </c>
+      <c r="B24" s="4">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A25" s="25" t="s">
+        <v>327</v>
+      </c>
+      <c r="B25" s="4">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A26" s="25" t="s">
+        <v>328</v>
+      </c>
+      <c r="B26" s="4">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A27" s="25" t="s">
+        <v>329</v>
+      </c>
+      <c r="B27" s="4">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" s="25" t="s">
+        <v>330</v>
+      </c>
+      <c r="B28" s="4">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" s="25" t="s">
+        <v>331</v>
+      </c>
+      <c r="B29" s="4">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" s="25" t="s">
+        <v>332</v>
+      </c>
+      <c r="B30" s="4">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" s="25" t="s">
+        <v>333</v>
+      </c>
+      <c r="B31" s="4">
+        <v>46218</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" s="25" t="s">
+        <v>334</v>
+      </c>
+      <c r="B32" s="4">
+        <v>46218</v>
       </c>
     </row>
   </sheetData>

--- a/Master/KODE DAN RESTO BOM NEW.xlsx
+++ b/Master/KODE DAN RESTO BOM NEW.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lenovo\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FORMAT DAN TEMPLATE\T013_Vba_Spit_data\DEX\Master\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E3D9739-68DB-4D8C-B8C2-769B3936A88B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28B8AF4E-46A8-499B-96AF-B210E97A300E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{2A27DFF0-1BDB-46C7-8D34-C6B2AB0C8283}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="2" xr2:uid="{2A27DFF0-1BDB-46C7-8D34-C6B2AB0C8283}"/>
   </bookViews>
   <sheets>
     <sheet name="KODE" sheetId="1" r:id="rId1"/>
@@ -26,23 +26,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="488" uniqueCount="342">
   <si>
     <t>NO</t>
   </si>
@@ -1059,6 +1048,15 @@
   </si>
   <si>
     <t>EXCLUDE_DATE</t>
+  </si>
+  <si>
+    <t>WCR</t>
+  </si>
+  <si>
+    <t>MLGSOE</t>
+  </si>
+  <si>
+    <t>1209.1-G.Malang - Soekarno Hatta (MLGSOE)</t>
   </si>
 </sst>
 </file>
@@ -1116,7 +1114,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1201,6 +1199,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFEA9999"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="5">
     <border>
@@ -1271,7 +1275,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1342,6 +1346,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="14" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1412,9 +1422,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2013 - 2022">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1452,7 +1462,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2013 - 2022">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1558,7 +1568,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2013 - 2022">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1700,7 +1710,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1709,14 +1719,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04EABAD4-117C-4DE8-B838-BB6A4F70CD80}">
   <dimension ref="A1:B22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>156</v>
       </c>
@@ -1724,7 +1734,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="14">
         <v>550064</v>
       </c>
@@ -1732,7 +1742,7 @@
         <v>550364</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="14">
         <v>550065</v>
       </c>
@@ -1740,7 +1750,7 @@
         <v>550365</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="14">
         <v>550080</v>
       </c>
@@ -1748,7 +1758,7 @@
         <v>550366</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="14">
         <v>550081</v>
       </c>
@@ -1756,7 +1766,7 @@
         <v>550367</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="14">
         <v>550260</v>
       </c>
@@ -1764,7 +1774,7 @@
         <v>550368</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="14">
         <v>550261</v>
       </c>
@@ -1772,7 +1782,7 @@
         <v>550369</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="14">
         <v>550262</v>
       </c>
@@ -1780,7 +1790,7 @@
         <v>550370</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="14">
         <v>550263</v>
       </c>
@@ -1788,7 +1798,7 @@
         <v>550371</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="14">
         <v>550264</v>
       </c>
@@ -1796,7 +1806,7 @@
         <v>550372</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="14">
         <v>550265</v>
       </c>
@@ -1804,7 +1814,7 @@
         <v>550373</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="14">
         <v>550266</v>
       </c>
@@ -1812,7 +1822,7 @@
         <v>550374</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="14">
         <v>550267</v>
       </c>
@@ -1820,7 +1830,7 @@
         <v>550375</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="14">
         <v>550268</v>
       </c>
@@ -1828,7 +1838,7 @@
         <v>550376</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="14">
         <v>550269</v>
       </c>
@@ -1836,7 +1846,7 @@
         <v>550377</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="14">
         <v>550270</v>
       </c>
@@ -1844,7 +1854,7 @@
         <v>550378</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="14">
         <v>550271</v>
       </c>
@@ -1852,7 +1862,7 @@
         <v>550379</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="14">
         <v>550146</v>
       </c>
@@ -1860,7 +1870,7 @@
         <v>550430</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="14">
         <v>550151</v>
       </c>
@@ -1868,7 +1878,7 @@
         <v>550431</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="14">
         <v>550152</v>
       </c>
@@ -1876,7 +1886,7 @@
         <v>550432</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="14">
         <v>550153</v>
       </c>
@@ -1884,7 +1894,7 @@
         <v>550433</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="14">
         <v>550154</v>
       </c>
@@ -1901,15 +1911,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB90F88C-CAFF-4807-B167-4FE3417BBD55}">
   <dimension ref="A1:D41"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.453125" customWidth="1"/>
-    <col min="3" max="3" width="9.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.42578125" customWidth="1"/>
+    <col min="3" max="3" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
         <v>158</v>
       </c>
@@ -1923,565 +1933,205 @@
         <v>157</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>234</v>
-      </c>
-      <c r="B2" s="4">
-        <v>46197</v>
-      </c>
-      <c r="C2" s="23">
-        <v>550004</v>
-      </c>
-      <c r="D2" s="23">
-        <v>550386</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>234</v>
-      </c>
-      <c r="B3" s="4">
-        <v>46197</v>
-      </c>
-      <c r="C3" s="23">
-        <v>550005</v>
-      </c>
-      <c r="D3" s="23">
-        <v>550387</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>234</v>
-      </c>
-      <c r="B4" s="4">
-        <v>46197</v>
-      </c>
-      <c r="C4" s="23">
-        <v>550007</v>
-      </c>
-      <c r="D4" s="23">
-        <v>550388</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>234</v>
-      </c>
-      <c r="B5" s="4">
-        <v>46197</v>
-      </c>
-      <c r="C5" s="23">
-        <v>550009</v>
-      </c>
-      <c r="D5" s="23">
-        <v>550389</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>234</v>
-      </c>
-      <c r="B6" s="4">
-        <v>46197</v>
-      </c>
-      <c r="C6" s="23">
-        <v>550011</v>
-      </c>
-      <c r="D6" s="23">
-        <v>550390</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>234</v>
-      </c>
-      <c r="B7" s="4">
-        <v>46197</v>
-      </c>
-      <c r="C7" s="23">
-        <v>550013</v>
-      </c>
-      <c r="D7" s="23">
-        <v>550391</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
-        <v>234</v>
-      </c>
-      <c r="B8" s="4">
-        <v>46197</v>
-      </c>
-      <c r="C8" s="23">
-        <v>550043</v>
-      </c>
-      <c r="D8" s="23">
-        <v>550392</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>234</v>
-      </c>
-      <c r="B9" s="4">
-        <v>46197</v>
-      </c>
-      <c r="C9" s="23">
-        <v>550045</v>
-      </c>
-      <c r="D9" s="23">
-        <v>550393</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
-        <v>234</v>
-      </c>
-      <c r="B10" s="4">
-        <v>46197</v>
-      </c>
-      <c r="C10" s="23">
-        <v>550047</v>
-      </c>
-      <c r="D10" s="23">
-        <v>550394</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
-        <v>234</v>
-      </c>
-      <c r="B11" s="4">
-        <v>46197</v>
-      </c>
-      <c r="C11" s="23">
-        <v>550049</v>
-      </c>
-      <c r="D11" s="23">
-        <v>550395</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
-        <v>234</v>
-      </c>
-      <c r="B12" s="4">
-        <v>46197</v>
-      </c>
-      <c r="C12" s="23">
-        <v>550055</v>
-      </c>
-      <c r="D12" s="23">
-        <v>550396</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>234</v>
-      </c>
-      <c r="B13" s="4">
-        <v>46197</v>
-      </c>
-      <c r="C13" s="23">
-        <v>550057</v>
-      </c>
-      <c r="D13" s="23">
-        <v>550397</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>234</v>
-      </c>
-      <c r="B14" s="4">
-        <v>46197</v>
-      </c>
-      <c r="C14" s="23">
-        <v>550059</v>
-      </c>
-      <c r="D14" s="23">
-        <v>550398</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>234</v>
-      </c>
-      <c r="B15" s="4">
-        <v>46197</v>
-      </c>
-      <c r="C15" s="23">
-        <v>550061</v>
-      </c>
-      <c r="D15" s="23">
-        <v>550399</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>234</v>
-      </c>
-      <c r="B16" s="4">
-        <v>46197</v>
-      </c>
-      <c r="C16" s="23">
-        <v>550063</v>
-      </c>
-      <c r="D16" s="23">
-        <v>550400</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>234</v>
-      </c>
-      <c r="B17" s="4">
-        <v>46197</v>
-      </c>
-      <c r="C17" s="23">
-        <v>550077</v>
-      </c>
-      <c r="D17" s="23">
-        <v>550401</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>234</v>
-      </c>
-      <c r="B18" s="4">
-        <v>46197</v>
-      </c>
-      <c r="C18" s="23">
-        <v>550093</v>
-      </c>
-      <c r="D18" s="23">
-        <v>550403</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>234</v>
-      </c>
-      <c r="B19" s="4">
-        <v>46197</v>
-      </c>
-      <c r="C19" s="23">
-        <v>550101</v>
-      </c>
-      <c r="D19" s="23">
-        <v>550404</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" t="s">
-        <v>234</v>
-      </c>
-      <c r="B20" s="4">
-        <v>46197</v>
-      </c>
-      <c r="C20" s="23">
-        <v>550147</v>
-      </c>
-      <c r="D20" s="23">
-        <v>550405</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" t="s">
-        <v>234</v>
-      </c>
-      <c r="B21" s="4">
-        <v>46197</v>
-      </c>
-      <c r="C21" s="23">
-        <v>550148</v>
-      </c>
-      <c r="D21" s="23">
-        <v>550406</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A22" t="s">
-        <v>234</v>
-      </c>
-      <c r="B22" s="4">
-        <v>46197</v>
-      </c>
-      <c r="C22" s="23">
-        <v>550149</v>
-      </c>
-      <c r="D22" s="23">
-        <v>550407</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A23" t="s">
-        <v>234</v>
-      </c>
-      <c r="B23" s="4">
-        <v>46197</v>
-      </c>
-      <c r="C23" s="23">
-        <v>550150</v>
-      </c>
-      <c r="D23" s="23">
-        <v>550408</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A24" t="s">
-        <v>234</v>
-      </c>
-      <c r="B24" s="4">
-        <v>46197</v>
-      </c>
-      <c r="C24" s="23">
-        <v>550155</v>
-      </c>
-      <c r="D24" s="23">
-        <v>550413</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A25" t="s">
-        <v>234</v>
-      </c>
-      <c r="B25" s="4">
-        <v>46197</v>
-      </c>
-      <c r="C25" s="23">
-        <v>550156</v>
-      </c>
-      <c r="D25" s="23">
-        <v>550414</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A26" t="s">
-        <v>234</v>
-      </c>
-      <c r="B26" s="4">
-        <v>46197</v>
-      </c>
-      <c r="C26" s="23">
-        <v>550157</v>
-      </c>
-      <c r="D26" s="23">
-        <v>550415</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A27" t="s">
-        <v>234</v>
-      </c>
-      <c r="B27" s="4">
-        <v>46197</v>
-      </c>
-      <c r="C27" s="23">
-        <v>550158</v>
-      </c>
-      <c r="D27" s="23">
-        <v>550416</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>234</v>
-      </c>
-      <c r="B28" s="4">
-        <v>46197</v>
-      </c>
-      <c r="C28" s="23">
-        <v>550367</v>
-      </c>
-      <c r="D28" s="23">
-        <v>550423</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>234</v>
-      </c>
-      <c r="B29" s="4">
-        <v>46197</v>
-      </c>
-      <c r="C29" s="23">
-        <v>550369</v>
-      </c>
-      <c r="D29" s="23">
-        <v>550424</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>234</v>
-      </c>
-      <c r="B30" s="4">
-        <v>46197</v>
-      </c>
-      <c r="C30" s="23">
-        <v>550371</v>
-      </c>
-      <c r="D30" s="23">
-        <v>550425</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>234</v>
-      </c>
-      <c r="B31" s="4">
-        <v>46197</v>
-      </c>
-      <c r="C31" s="23">
-        <v>550373</v>
-      </c>
-      <c r="D31" s="23">
-        <v>550426</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>234</v>
-      </c>
-      <c r="B32" s="4">
-        <v>46197</v>
-      </c>
-      <c r="C32" s="23">
-        <v>550375</v>
-      </c>
-      <c r="D32" s="23">
-        <v>550427</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>234</v>
-      </c>
-      <c r="B33" s="4">
-        <v>46197</v>
-      </c>
-      <c r="C33" s="23">
-        <v>550377</v>
-      </c>
-      <c r="D33" s="23">
-        <v>550428</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>234</v>
-      </c>
-      <c r="B34" s="4">
-        <v>46197</v>
-      </c>
-      <c r="C34" s="23">
-        <v>550379</v>
-      </c>
-      <c r="D34" s="23">
-        <v>550429</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>234</v>
-      </c>
-      <c r="B35" s="4">
-        <v>46197</v>
-      </c>
-      <c r="C35" s="23">
-        <v>550151</v>
-      </c>
-      <c r="D35" s="23">
-        <v>550435</v>
-      </c>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>234</v>
-      </c>
-      <c r="B36" s="4">
-        <v>46197</v>
-      </c>
-      <c r="C36" s="23">
-        <v>550152</v>
-      </c>
-      <c r="D36" s="23">
-        <v>550436</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>234</v>
-      </c>
-      <c r="B37" s="4">
-        <v>46197</v>
-      </c>
-      <c r="C37" s="23">
-        <v>550153</v>
-      </c>
-      <c r="D37" s="23">
-        <v>550437</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>234</v>
-      </c>
-      <c r="B38" s="4">
-        <v>46197</v>
-      </c>
-      <c r="C38" s="23">
-        <v>550154</v>
-      </c>
-      <c r="D38" s="23">
-        <v>550438</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>234</v>
-      </c>
-      <c r="B39" s="4">
-        <v>46197</v>
-      </c>
-      <c r="C39" s="23">
-        <v>550146</v>
-      </c>
-      <c r="D39" s="23">
-        <v>550430</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>234</v>
-      </c>
-      <c r="B40" s="4">
-        <v>46197</v>
-      </c>
-      <c r="C40" s="23">
-        <v>550064</v>
-      </c>
-      <c r="D40" s="23">
-        <v>550364</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>234</v>
-      </c>
-      <c r="B41" s="4">
-        <v>46197</v>
-      </c>
-      <c r="C41" s="23">
-        <v>550065</v>
-      </c>
-      <c r="D41" s="23">
-        <v>550365</v>
-      </c>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B2" s="4"/>
+      <c r="C2" s="23"/>
+      <c r="D2" s="23"/>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B3" s="4"/>
+      <c r="C3" s="23"/>
+      <c r="D3" s="23"/>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B4" s="4"/>
+      <c r="C4" s="23"/>
+      <c r="D4" s="23"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B5" s="4"/>
+      <c r="C5" s="23"/>
+      <c r="D5" s="23"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B6" s="4"/>
+      <c r="C6" s="23"/>
+      <c r="D6" s="23"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B7" s="4"/>
+      <c r="C7" s="23"/>
+      <c r="D7" s="23"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B8" s="4"/>
+      <c r="C8" s="23"/>
+      <c r="D8" s="23"/>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B9" s="4"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B10" s="4"/>
+      <c r="C10" s="23"/>
+      <c r="D10" s="23"/>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B11" s="4"/>
+      <c r="C11" s="23"/>
+      <c r="D11" s="23"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B12" s="4"/>
+      <c r="C12" s="23"/>
+      <c r="D12" s="23"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B13" s="4"/>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B14" s="4"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B15" s="4"/>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B16" s="4"/>
+      <c r="C16" s="23"/>
+      <c r="D16" s="23"/>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B17" s="4"/>
+      <c r="C17" s="23"/>
+      <c r="D17" s="23"/>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B18" s="4"/>
+      <c r="C18" s="23"/>
+      <c r="D18" s="23"/>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B19" s="4"/>
+      <c r="C19" s="23"/>
+      <c r="D19" s="23"/>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B20" s="4"/>
+      <c r="C20" s="23"/>
+      <c r="D20" s="23"/>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B21" s="4"/>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B22" s="4"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B23" s="4"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B24" s="4"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="23"/>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B25" s="4"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="23"/>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B26" s="4"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="23"/>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B27" s="4"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B28" s="4"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="23"/>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B29" s="4"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="23"/>
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B30" s="4"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="23"/>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B31" s="4"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="23"/>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B32" s="4"/>
+      <c r="C32" s="23"/>
+      <c r="D32" s="23"/>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B33" s="4"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="23"/>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B34" s="4"/>
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B35" s="4"/>
+      <c r="C35" s="23"/>
+      <c r="D35" s="23"/>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B36" s="4"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="23"/>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B37" s="4"/>
+      <c r="C37" s="23"/>
+      <c r="D37" s="23"/>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B38" s="4"/>
+      <c r="C38" s="23"/>
+      <c r="D38" s="23"/>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B39" s="4"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="23"/>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B40" s="4"/>
+      <c r="C40" s="23"/>
+      <c r="D40" s="23"/>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B41" s="4"/>
+      <c r="C41" s="23"/>
+      <c r="D41" s="23"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="A1:B1">
@@ -2499,17 +2149,17 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C0933A7F-4C29-4A64-8B36-B4F9E885B333}">
-  <dimension ref="A1:F115"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:F116"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="41.54296875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="41.5703125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2529,7 +2179,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -2549,7 +2199,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <f t="shared" ref="A3:A51" si="0">1+A2</f>
         <v>2</v>
@@ -2570,7 +2220,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <f t="shared" si="0"/>
         <v>3</v>
@@ -2591,7 +2241,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
@@ -2612,7 +2262,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
@@ -2633,7 +2283,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
@@ -2654,7 +2304,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
@@ -2675,7 +2325,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
@@ -2696,7 +2346,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
@@ -2717,7 +2367,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
@@ -2738,7 +2388,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <f t="shared" si="0"/>
         <v>11</v>
@@ -2759,7 +2409,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2">
         <f t="shared" si="0"/>
         <v>12</v>
@@ -2780,7 +2430,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
         <f t="shared" si="0"/>
         <v>13</v>
@@ -2801,7 +2451,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="2">
         <f t="shared" si="0"/>
         <v>14</v>
@@ -2822,7 +2472,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
         <f t="shared" si="0"/>
         <v>15</v>
@@ -2843,7 +2493,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2">
         <f t="shared" si="0"/>
         <v>16</v>
@@ -2864,7 +2514,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2">
         <f t="shared" si="0"/>
         <v>17</v>
@@ -2885,7 +2535,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2">
         <f t="shared" si="0"/>
         <v>18</v>
@@ -2906,7 +2556,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2">
         <f t="shared" si="0"/>
         <v>19</v>
@@ -2927,7 +2577,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="2">
         <f t="shared" si="0"/>
         <v>20</v>
@@ -2948,7 +2598,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="2">
         <f t="shared" si="0"/>
         <v>21</v>
@@ -2969,7 +2619,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="2">
         <f t="shared" si="0"/>
         <v>22</v>
@@ -2990,7 +2640,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="2">
         <f t="shared" si="0"/>
         <v>23</v>
@@ -3011,7 +2661,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="2">
         <f t="shared" si="0"/>
         <v>24</v>
@@ -3032,7 +2682,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="2">
         <f t="shared" si="0"/>
         <v>25</v>
@@ -3053,7 +2703,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="2">
         <f t="shared" si="0"/>
         <v>26</v>
@@ -3074,7 +2724,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="2">
         <f t="shared" si="0"/>
         <v>27</v>
@@ -3095,7 +2745,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="2">
         <f t="shared" si="0"/>
         <v>28</v>
@@ -3116,7 +2766,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="2">
         <f t="shared" si="0"/>
         <v>29</v>
@@ -3137,7 +2787,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="2">
         <f t="shared" si="0"/>
         <v>30</v>
@@ -3158,7 +2808,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="2">
         <f t="shared" si="0"/>
         <v>31</v>
@@ -3179,7 +2829,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="2">
         <f t="shared" si="0"/>
         <v>32</v>
@@ -3200,7 +2850,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
         <f t="shared" si="0"/>
         <v>33</v>
@@ -3221,7 +2871,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
         <f t="shared" si="0"/>
         <v>34</v>
@@ -3242,7 +2892,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="2">
         <f t="shared" si="0"/>
         <v>35</v>
@@ -3263,7 +2913,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="2">
         <f t="shared" si="0"/>
         <v>36</v>
@@ -3284,7 +2934,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="2">
         <f t="shared" si="0"/>
         <v>37</v>
@@ -3305,7 +2955,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="2">
         <f t="shared" si="0"/>
         <v>38</v>
@@ -3326,7 +2976,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="2">
         <f t="shared" si="0"/>
         <v>39</v>
@@ -3347,7 +2997,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="2">
         <f t="shared" si="0"/>
         <v>40</v>
@@ -3368,7 +3018,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="2">
         <f t="shared" si="0"/>
         <v>41</v>
@@ -3389,7 +3039,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="2">
         <f t="shared" si="0"/>
         <v>42</v>
@@ -3410,7 +3060,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
         <f t="shared" si="0"/>
         <v>43</v>
@@ -3431,7 +3081,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="2">
         <f t="shared" si="0"/>
         <v>44</v>
@@ -3452,7 +3102,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
         <f t="shared" si="0"/>
         <v>45</v>
@@ -3473,7 +3123,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="2">
         <f t="shared" si="0"/>
         <v>46</v>
@@ -3494,7 +3144,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
         <f t="shared" si="0"/>
         <v>47</v>
@@ -3515,7 +3165,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="2">
         <f t="shared" si="0"/>
         <v>48</v>
@@ -3536,7 +3186,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
         <f t="shared" si="0"/>
         <v>49</v>
@@ -3557,7 +3207,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="2">
         <f t="shared" si="0"/>
         <v>50</v>
@@ -3578,7 +3228,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
         <v>51</v>
       </c>
@@ -3598,7 +3248,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="2">
         <v>52</v>
       </c>
@@ -3619,7 +3269,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="2">
         <v>53</v>
       </c>
@@ -3640,7 +3290,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="2">
         <v>54</v>
       </c>
@@ -3661,7 +3311,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="2">
         <v>55</v>
       </c>
@@ -3682,7 +3332,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="2">
         <v>56</v>
       </c>
@@ -3703,7 +3353,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="2">
         <v>57</v>
       </c>
@@ -3724,7 +3374,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="2">
         <v>58</v>
       </c>
@@ -3745,7 +3395,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="2">
         <v>59</v>
       </c>
@@ -3766,7 +3416,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="2">
         <v>60</v>
       </c>
@@ -3787,7 +3437,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="2">
         <v>61</v>
       </c>
@@ -3808,7 +3458,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="2">
         <v>62</v>
       </c>
@@ -3829,7 +3479,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="17">
         <f>1+A61</f>
         <v>61</v>
@@ -3851,7 +3501,7 @@
         <v>1053.BGRPAD</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="19">
         <f t="shared" ref="A65:A115" si="2">1+A64</f>
         <v>62</v>
@@ -3873,7 +3523,7 @@
         <v>1074.BGRTAJ</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="19">
         <f t="shared" si="2"/>
         <v>63</v>
@@ -3895,7 +3545,7 @@
         <v>1079.BGRSAP</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="19">
         <f t="shared" si="2"/>
         <v>64</v>
@@ -3917,7 +3567,7 @@
         <v>1100.BGRABD</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="19">
         <f t="shared" si="2"/>
         <v>65</v>
@@ -3939,7 +3589,7 @@
         <v>1112.BGRSHO</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="19">
         <f t="shared" si="2"/>
         <v>66</v>
@@ -3961,7 +3611,7 @@
         <v>1190.BGRBAT</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="19">
         <f t="shared" si="2"/>
         <v>67</v>
@@ -3982,7 +3632,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="19">
         <f t="shared" si="2"/>
         <v>68</v>
@@ -4003,7 +3653,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="19">
         <f t="shared" si="2"/>
         <v>69</v>
@@ -4024,7 +3674,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="19">
         <f t="shared" si="2"/>
         <v>70</v>
@@ -4045,7 +3695,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="19">
         <f t="shared" si="2"/>
         <v>71</v>
@@ -4066,7 +3716,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="19">
         <f t="shared" si="2"/>
         <v>72</v>
@@ -4087,7 +3737,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="19">
         <f t="shared" si="2"/>
         <v>73</v>
@@ -4108,7 +3758,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="19">
         <f t="shared" si="2"/>
         <v>74</v>
@@ -4129,7 +3779,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="19">
         <f t="shared" si="2"/>
         <v>75</v>
@@ -4150,7 +3800,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="19">
         <f t="shared" si="2"/>
         <v>76</v>
@@ -4171,7 +3821,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="19">
         <f t="shared" si="2"/>
         <v>77</v>
@@ -4192,7 +3842,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="19">
         <f t="shared" si="2"/>
         <v>78</v>
@@ -4213,7 +3863,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="19">
         <v>79</v>
       </c>
@@ -4233,7 +3883,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="19">
         <f t="shared" si="2"/>
         <v>80</v>
@@ -4254,7 +3904,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="19">
         <f t="shared" si="2"/>
         <v>81</v>
@@ -4275,7 +3925,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="19">
         <f t="shared" si="2"/>
         <v>82</v>
@@ -4296,7 +3946,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="19">
         <f t="shared" si="2"/>
         <v>83</v>
@@ -4317,7 +3967,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="19">
         <f t="shared" si="2"/>
         <v>84</v>
@@ -4338,7 +3988,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="19">
         <v>80</v>
       </c>
@@ -4358,7 +4008,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="19">
         <f t="shared" si="2"/>
         <v>81</v>
@@ -4379,7 +4029,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="19">
         <f t="shared" si="2"/>
         <v>82</v>
@@ -4400,7 +4050,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="19">
         <f t="shared" si="2"/>
         <v>83</v>
@@ -4421,7 +4071,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="19">
         <f t="shared" si="2"/>
         <v>84</v>
@@ -4442,7 +4092,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="19">
         <f t="shared" si="2"/>
         <v>85</v>
@@ -4463,7 +4113,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="19">
         <v>81</v>
       </c>
@@ -4483,7 +4133,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="19">
         <f t="shared" si="2"/>
         <v>82</v>
@@ -4504,7 +4154,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="19">
         <f t="shared" si="2"/>
         <v>83</v>
@@ -4525,7 +4175,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="19">
         <f t="shared" si="2"/>
         <v>84</v>
@@ -4546,7 +4196,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="19">
         <f t="shared" si="2"/>
         <v>85</v>
@@ -4567,7 +4217,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="19">
         <f t="shared" si="2"/>
         <v>86</v>
@@ -4588,7 +4238,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="19">
         <v>82</v>
       </c>
@@ -4608,7 +4258,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="19">
         <f t="shared" si="2"/>
         <v>83</v>
@@ -4629,7 +4279,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="19">
         <f t="shared" si="2"/>
         <v>84</v>
@@ -4650,7 +4300,7 @@
         <v>324</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="19">
         <f t="shared" si="2"/>
         <v>85</v>
@@ -4671,7 +4321,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="19">
         <f t="shared" si="2"/>
         <v>86</v>
@@ -4692,7 +4342,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="19">
         <f t="shared" si="2"/>
         <v>87</v>
@@ -4713,7 +4363,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="19">
         <v>83</v>
       </c>
@@ -4733,7 +4383,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="19">
         <f t="shared" si="2"/>
         <v>84</v>
@@ -4754,7 +4404,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="19">
         <f t="shared" si="2"/>
         <v>85</v>
@@ -4775,7 +4425,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="19">
         <f t="shared" si="2"/>
         <v>86</v>
@@ -4796,7 +4446,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="19">
         <f t="shared" si="2"/>
         <v>87</v>
@@ -4817,7 +4467,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="19">
         <f t="shared" si="2"/>
         <v>88</v>
@@ -4838,7 +4488,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="19">
         <v>84</v>
       </c>
@@ -4858,7 +4508,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="19">
         <f t="shared" si="2"/>
         <v>85</v>
@@ -4879,7 +4529,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="19">
         <f t="shared" si="2"/>
         <v>86</v>
@@ -4900,7 +4550,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="19">
         <f t="shared" si="2"/>
         <v>87</v>
@@ -4921,8 +4571,28 @@
         <v>337</v>
       </c>
     </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A116" s="19">
+        <v>88</v>
+      </c>
+      <c r="B116" s="26" t="s">
+        <v>339</v>
+      </c>
+      <c r="C116" s="26" t="s">
+        <v>340</v>
+      </c>
+      <c r="D116" s="26" t="s">
+        <v>341</v>
+      </c>
+      <c r="E116" s="27">
+        <v>46197</v>
+      </c>
+      <c r="F116" s="25" t="s">
+        <v>234</v>
+      </c>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="D83:D115">
+  <conditionalFormatting sqref="D83:D116">
     <cfRule type="duplicateValues" dxfId="1" priority="6"/>
     <cfRule type="duplicateValues" dxfId="0" priority="7"/>
   </conditionalFormatting>
@@ -4933,13 +4603,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{620FB88A-C9C3-47FD-BB4D-39DF868892A8}">
   <dimension ref="A1:B32"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>158</v>
       </c>
@@ -4947,7 +4617,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>232</v>
       </c>
@@ -4955,7 +4625,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>233</v>
       </c>
@@ -4963,7 +4633,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="25" t="s">
         <v>237</v>
       </c>
@@ -4971,7 +4641,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="25" t="s">
         <v>306</v>
       </c>
@@ -4979,7 +4649,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="25" t="s">
         <v>307</v>
       </c>
@@ -4987,7 +4657,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="25" t="s">
         <v>308</v>
       </c>
@@ -4995,7 +4665,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
         <v>309</v>
       </c>
@@ -5003,7 +4673,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="25" t="s">
         <v>310</v>
       </c>
@@ -5011,7 +4681,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="25" t="s">
         <v>311</v>
       </c>
@@ -5019,7 +4689,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="25" t="s">
         <v>312</v>
       </c>
@@ -5027,7 +4697,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="25" t="s">
         <v>314</v>
       </c>
@@ -5035,7 +4705,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="25" t="s">
         <v>315</v>
       </c>
@@ -5043,7 +4713,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="25" t="s">
         <v>316</v>
       </c>
@@ -5051,7 +4721,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="25" t="s">
         <v>317</v>
       </c>
@@ -5059,7 +4729,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="25" t="s">
         <v>318</v>
       </c>
@@ -5067,7 +4737,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
         <v>319</v>
       </c>
@@ -5075,7 +4745,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="25" t="s">
         <v>320</v>
       </c>
@@ -5083,7 +4753,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="25" t="s">
         <v>321</v>
       </c>
@@ -5091,7 +4761,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" s="25" t="s">
         <v>322</v>
       </c>
@@ -5099,7 +4769,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="25" t="s">
         <v>323</v>
       </c>
@@ -5107,7 +4777,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="25" t="s">
         <v>324</v>
       </c>
@@ -5115,7 +4785,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="25" t="s">
         <v>325</v>
       </c>
@@ -5123,7 +4793,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" s="25" t="s">
         <v>326</v>
       </c>
@@ -5131,7 +4801,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" s="25" t="s">
         <v>327</v>
       </c>
@@ -5139,7 +4809,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="25" t="s">
         <v>328</v>
       </c>
@@ -5147,7 +4817,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" s="25" t="s">
         <v>329</v>
       </c>
@@ -5155,7 +4825,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" s="25" t="s">
         <v>330</v>
       </c>
@@ -5163,7 +4833,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="25" t="s">
         <v>331</v>
       </c>
@@ -5171,7 +4841,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="25" t="s">
         <v>332</v>
       </c>
@@ -5179,7 +4849,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="25" t="s">
         <v>333</v>
       </c>
@@ -5187,7 +4857,7 @@
         <v>46218</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="25" t="s">
         <v>334</v>
       </c>
